--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -772,13 +772,13 @@
     <t>Shiaijo B</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>White</t>
   </si>
   <si>
     <t xml:space="preserve">1. </t>
@@ -6952,28 +6952,28 @@
       <c r="O4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L5" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O5" s="24" t="s">
+      <c r="O5" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -6981,10 +6981,10 @@
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I6" s="21" t="str">
-        <f>data!$B$50</f>
+        <f>data!$B$51</f>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -6992,12 +6992,12 @@
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
       <c r="O6" s="21" t="str">
-        <f>data!$B$51</f>
+        <f>data!$B$50</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -7005,10 +7005,10 @@
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
       <c r="G7" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I7" s="21" t="str">
-        <f>data!$B$50</f>
+        <f>data!$B$52</f>
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21"/>
@@ -7016,12 +7016,12 @@
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
       <c r="O7" s="21" t="str">
-        <f>data!$B$52</f>
+        <f>data!$B$50</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -7029,10 +7029,10 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I8" s="21" t="str">
-        <f>data!$B$51</f>
+        <f>data!$B$52</f>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
@@ -7040,7 +7040,7 @@
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
       <c r="O8" s="21" t="str">
-        <f>data!$B$52</f>
+        <f>data!$B$51</f>
       </c>
     </row>
     <row r="10">
@@ -7094,28 +7094,28 @@
       <c r="O15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L16" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O16" s="24" t="s">
+      <c r="O16" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -7123,10 +7123,10 @@
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$6</f>
       </c>
       <c r="I17" s="21" t="str">
-        <f>data!$B$53</f>
+        <f>data!$B$54</f>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
@@ -7134,12 +7134,12 @@
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
       <c r="O17" s="21" t="str">
-        <f>data!$B$54</f>
+        <f>data!$B$53</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -7147,10 +7147,10 @@
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$6</f>
       </c>
       <c r="I18" s="21" t="str">
-        <f>data!$B$53</f>
+        <f>data!$B$55</f>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
@@ -7158,12 +7158,12 @@
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="21" t="str">
-        <f>data!$B$55</f>
+        <f>data!$B$53</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -7171,10 +7171,10 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$54</f>
+        <f>data!$B$55</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -7182,7 +7182,7 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$55</f>
+        <f>data!$B$54</f>
       </c>
     </row>
     <row r="21">
@@ -7236,28 +7236,28 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L27" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O27" s="24" t="s">
+      <c r="O27" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$10</f>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -7265,10 +7265,10 @@
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$9</f>
       </c>
       <c r="I28" s="21" t="str">
-        <f>data!$B$56</f>
+        <f>data!$B$57</f>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
@@ -7276,12 +7276,12 @@
       <c r="M28" s="21"/>
       <c r="N28" s="21"/>
       <c r="O28" s="21" t="str">
-        <f>data!$B$57</f>
+        <f>data!$B$56</f>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$11</f>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -7289,10 +7289,10 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
       <c r="I29" s="21" t="str">
-        <f>data!$B$56</f>
+        <f>data!$B$58</f>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
@@ -7300,12 +7300,12 @@
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21" t="str">
-        <f>data!$B$58</f>
+        <f>data!$B$56</f>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -7313,10 +7313,10 @@
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
       <c r="G30" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I30" s="21" t="str">
-        <f>data!$B$57</f>
+        <f>data!$B$58</f>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
@@ -7324,7 +7324,7 @@
       <c r="M30" s="21"/>
       <c r="N30" s="21"/>
       <c r="O30" s="21" t="str">
-        <f>data!$B$58</f>
+        <f>data!$B$57</f>
       </c>
     </row>
     <row r="32">
@@ -7378,28 +7378,28 @@
       <c r="O37" s="20"/>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D38" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L38" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O38" s="24" t="s">
+      <c r="O38" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$13</f>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -7407,10 +7407,10 @@
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$12</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$59</f>
+        <f>data!$B$60</f>
       </c>
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
@@ -7418,12 +7418,12 @@
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
       <c r="O39" s="21" t="str">
-        <f>data!$B$60</f>
+        <f>data!$B$59</f>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -7431,10 +7431,10 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$12</f>
       </c>
       <c r="I40" s="21" t="str">
-        <f>data!$B$59</f>
+        <f>data!$B$61</f>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -7442,12 +7442,12 @@
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21" t="str">
-        <f>data!$B$61</f>
+        <f>data!$B$59</f>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -7455,10 +7455,10 @@
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I41" s="21" t="str">
-        <f>data!$B$60</f>
+        <f>data!$B$61</f>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
@@ -7466,7 +7466,7 @@
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21" t="str">
-        <f>data!$B$61</f>
+        <f>data!$B$60</f>
       </c>
     </row>
     <row r="43">
@@ -7520,28 +7520,28 @@
       <c r="O48" s="20"/>
     </row>
     <row r="49">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D49" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="G49" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I49" s="23" t="s">
+      <c r="I49" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L49" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O49" s="24" t="s">
+      <c r="O49" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$16</f>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -7549,10 +7549,10 @@
       <c r="E50" s="21"/>
       <c r="F50" s="21"/>
       <c r="G50" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$15</f>
       </c>
       <c r="I50" s="21" t="str">
-        <f>data!$B$62</f>
+        <f>data!$B$63</f>
       </c>
       <c r="J50" s="21"/>
       <c r="K50" s="21"/>
@@ -7560,12 +7560,12 @@
       <c r="M50" s="21"/>
       <c r="N50" s="21"/>
       <c r="O50" s="21" t="str">
-        <f>data!$B$63</f>
+        <f>data!$B$62</f>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$17</f>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -7573,10 +7573,10 @@
       <c r="E51" s="21"/>
       <c r="F51" s="21"/>
       <c r="G51" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$15</f>
       </c>
       <c r="I51" s="21" t="str">
-        <f>data!$B$62</f>
+        <f>data!$B$64</f>
       </c>
       <c r="J51" s="21"/>
       <c r="K51" s="21"/>
@@ -7584,12 +7584,12 @@
       <c r="M51" s="21"/>
       <c r="N51" s="21"/>
       <c r="O51" s="21" t="str">
-        <f>data!$B$64</f>
+        <f>data!$B$62</f>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$17</f>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -7597,10 +7597,10 @@
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
       <c r="G52" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I52" s="21" t="str">
-        <f>data!$B$63</f>
+        <f>data!$B$64</f>
       </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
@@ -7608,7 +7608,7 @@
       <c r="M52" s="21"/>
       <c r="N52" s="21"/>
       <c r="O52" s="21" t="str">
-        <f>data!$B$64</f>
+        <f>data!$B$63</f>
       </c>
     </row>
     <row r="54">
@@ -7662,28 +7662,28 @@
       <c r="O59" s="20"/>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G60" s="24" t="s">
+      <c r="G60" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I60" s="23" t="s">
+      <c r="I60" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L60" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O60" s="24" t="s">
+      <c r="O60" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$19</f>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -7691,10 +7691,10 @@
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
       <c r="G61" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$18</f>
       </c>
       <c r="I61" s="21" t="str">
-        <f>data!$B$65</f>
+        <f>data!$B$66</f>
       </c>
       <c r="J61" s="21"/>
       <c r="K61" s="21"/>
@@ -7702,12 +7702,12 @@
       <c r="M61" s="21"/>
       <c r="N61" s="21"/>
       <c r="O61" s="21" t="str">
-        <f>data!$B$66</f>
+        <f>data!$B$65</f>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$20</f>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -7715,10 +7715,10 @@
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
       <c r="G62" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$18</f>
       </c>
       <c r="I62" s="21" t="str">
-        <f>data!$B$65</f>
+        <f>data!$B$67</f>
       </c>
       <c r="J62" s="21"/>
       <c r="K62" s="21"/>
@@ -7726,12 +7726,12 @@
       <c r="M62" s="21"/>
       <c r="N62" s="21"/>
       <c r="O62" s="21" t="str">
-        <f>data!$B$67</f>
+        <f>data!$B$65</f>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$20</f>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -7739,10 +7739,10 @@
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
       <c r="G63" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$19</f>
       </c>
       <c r="I63" s="21" t="str">
-        <f>data!$B$66</f>
+        <f>data!$B$67</f>
       </c>
       <c r="J63" s="21"/>
       <c r="K63" s="21"/>
@@ -7750,7 +7750,7 @@
       <c r="M63" s="21"/>
       <c r="N63" s="21"/>
       <c r="O63" s="21" t="str">
-        <f>data!$B$67</f>
+        <f>data!$B$66</f>
       </c>
     </row>
     <row r="65">
@@ -7804,28 +7804,28 @@
       <c r="O70" s="20"/>
     </row>
     <row r="71">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D71" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G71" s="24" t="s">
+      <c r="G71" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I71" s="23" t="s">
+      <c r="I71" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L71" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O71" s="24" t="s">
+      <c r="O71" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$22</f>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="21"/>
@@ -7833,10 +7833,10 @@
       <c r="E72" s="21"/>
       <c r="F72" s="21"/>
       <c r="G72" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$21</f>
       </c>
       <c r="I72" s="21" t="str">
-        <f>data!$B$68</f>
+        <f>data!$B$69</f>
       </c>
       <c r="J72" s="21"/>
       <c r="K72" s="21"/>
@@ -7844,12 +7844,12 @@
       <c r="M72" s="21"/>
       <c r="N72" s="21"/>
       <c r="O72" s="21" t="str">
-        <f>data!$B$69</f>
+        <f>data!$B$68</f>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$23</f>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="21"/>
@@ -7857,10 +7857,10 @@
       <c r="E73" s="21"/>
       <c r="F73" s="21"/>
       <c r="G73" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$21</f>
       </c>
       <c r="I73" s="21" t="str">
-        <f>data!$B$68</f>
+        <f>data!$B$70</f>
       </c>
       <c r="J73" s="21"/>
       <c r="K73" s="21"/>
@@ -7868,12 +7868,12 @@
       <c r="M73" s="21"/>
       <c r="N73" s="21"/>
       <c r="O73" s="21" t="str">
-        <f>data!$B$70</f>
+        <f>data!$B$68</f>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$23</f>
       </c>
       <c r="B74" s="21"/>
       <c r="C74" s="21"/>
@@ -7881,10 +7881,10 @@
       <c r="E74" s="21"/>
       <c r="F74" s="21"/>
       <c r="G74" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I74" s="21" t="str">
-        <f>data!$B$69</f>
+        <f>data!$B$70</f>
       </c>
       <c r="J74" s="21"/>
       <c r="K74" s="21"/>
@@ -7892,7 +7892,7 @@
       <c r="M74" s="21"/>
       <c r="N74" s="21"/>
       <c r="O74" s="21" t="str">
-        <f>data!$B$70</f>
+        <f>data!$B$69</f>
       </c>
     </row>
     <row r="76">
@@ -7946,28 +7946,28 @@
       <c r="O81" s="20"/>
     </row>
     <row r="82">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D82" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G82" s="24" t="s">
+      <c r="G82" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I82" s="23" t="s">
+      <c r="I82" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L82" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O82" s="24" t="s">
+      <c r="O82" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$25</f>
       </c>
       <c r="B83" s="21"/>
       <c r="C83" s="21"/>
@@ -7975,10 +7975,10 @@
       <c r="E83" s="21"/>
       <c r="F83" s="21"/>
       <c r="G83" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$24</f>
       </c>
       <c r="I83" s="21" t="str">
-        <f>data!$B$71</f>
+        <f>data!$B$72</f>
       </c>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
@@ -7986,12 +7986,12 @@
       <c r="M83" s="21"/>
       <c r="N83" s="21"/>
       <c r="O83" s="21" t="str">
-        <f>data!$B$72</f>
+        <f>data!$B$71</f>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$26</f>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="21"/>
@@ -7999,10 +7999,10 @@
       <c r="E84" s="21"/>
       <c r="F84" s="21"/>
       <c r="G84" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$24</f>
       </c>
       <c r="I84" s="21" t="str">
-        <f>data!$B$71</f>
+        <f>data!$B$73</f>
       </c>
       <c r="J84" s="21"/>
       <c r="K84" s="21"/>
@@ -8010,12 +8010,12 @@
       <c r="M84" s="21"/>
       <c r="N84" s="21"/>
       <c r="O84" s="21" t="str">
-        <f>data!$B$73</f>
+        <f>data!$B$71</f>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$26</f>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="21"/>
@@ -8023,10 +8023,10 @@
       <c r="E85" s="21"/>
       <c r="F85" s="21"/>
       <c r="G85" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$25</f>
       </c>
       <c r="I85" s="21" t="str">
-        <f>data!$B$72</f>
+        <f>data!$B$73</f>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -8034,7 +8034,7 @@
       <c r="M85" s="21"/>
       <c r="N85" s="21"/>
       <c r="O85" s="21" t="str">
-        <f>data!$B$73</f>
+        <f>data!$B$72</f>
       </c>
     </row>
     <row r="87">
@@ -8088,28 +8088,28 @@
       <c r="O92" s="20"/>
     </row>
     <row r="93">
-      <c r="A93" s="23" t="s">
+      <c r="A93" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D93" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G93" s="24" t="s">
+      <c r="G93" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I93" s="23" t="s">
+      <c r="I93" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L93" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O93" s="24" t="s">
+      <c r="O93" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="21" t="str">
-        <f>data!$B$27</f>
+        <f>data!$B$28</f>
       </c>
       <c r="B94" s="21"/>
       <c r="C94" s="21"/>
@@ -8117,10 +8117,10 @@
       <c r="E94" s="21"/>
       <c r="F94" s="21"/>
       <c r="G94" s="21" t="str">
-        <f>data!$B$28</f>
+        <f>data!$B$27</f>
       </c>
       <c r="I94" s="21" t="str">
-        <f>data!$B$74</f>
+        <f>data!$B$75</f>
       </c>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
@@ -8128,12 +8128,12 @@
       <c r="M94" s="21"/>
       <c r="N94" s="21"/>
       <c r="O94" s="21" t="str">
-        <f>data!$B$75</f>
+        <f>data!$B$74</f>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="21" t="str">
-        <f>data!$B$27</f>
+        <f>data!$B$29</f>
       </c>
       <c r="B95" s="21"/>
       <c r="C95" s="21"/>
@@ -8141,10 +8141,10 @@
       <c r="E95" s="21"/>
       <c r="F95" s="21"/>
       <c r="G95" s="21" t="str">
-        <f>data!$B$29</f>
+        <f>data!$B$27</f>
       </c>
       <c r="I95" s="21" t="str">
-        <f>data!$B$74</f>
+        <f>data!$B$76</f>
       </c>
       <c r="J95" s="21"/>
       <c r="K95" s="21"/>
@@ -8152,12 +8152,12 @@
       <c r="M95" s="21"/>
       <c r="N95" s="21"/>
       <c r="O95" s="21" t="str">
-        <f>data!$B$76</f>
+        <f>data!$B$74</f>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="21" t="str">
-        <f>data!$B$28</f>
+        <f>data!$B$29</f>
       </c>
       <c r="B96" s="21"/>
       <c r="C96" s="21"/>
@@ -8165,10 +8165,10 @@
       <c r="E96" s="21"/>
       <c r="F96" s="21"/>
       <c r="G96" s="21" t="str">
-        <f>data!$B$29</f>
+        <f>data!$B$28</f>
       </c>
       <c r="I96" s="21" t="str">
-        <f>data!$B$75</f>
+        <f>data!$B$76</f>
       </c>
       <c r="J96" s="21"/>
       <c r="K96" s="21"/>
@@ -8176,7 +8176,7 @@
       <c r="M96" s="21"/>
       <c r="N96" s="21"/>
       <c r="O96" s="21" t="str">
-        <f>data!$B$76</f>
+        <f>data!$B$75</f>
       </c>
     </row>
     <row r="98">
@@ -8230,28 +8230,28 @@
       <c r="O103" s="20"/>
     </row>
     <row r="104">
-      <c r="A104" s="23" t="s">
+      <c r="A104" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D104" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G104" s="24" t="s">
+      <c r="G104" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I104" s="23" t="s">
+      <c r="I104" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L104" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O104" s="24" t="s">
+      <c r="O104" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="21" t="str">
-        <f>data!$B$30</f>
+        <f>data!$B$31</f>
       </c>
       <c r="B105" s="21"/>
       <c r="C105" s="21"/>
@@ -8259,10 +8259,10 @@
       <c r="E105" s="21"/>
       <c r="F105" s="21"/>
       <c r="G105" s="21" t="str">
-        <f>data!$B$31</f>
+        <f>data!$B$30</f>
       </c>
       <c r="I105" s="21" t="str">
-        <f>data!$B$77</f>
+        <f>data!$B$78</f>
       </c>
       <c r="J105" s="21"/>
       <c r="K105" s="21"/>
@@ -8270,12 +8270,12 @@
       <c r="M105" s="21"/>
       <c r="N105" s="21"/>
       <c r="O105" s="21" t="str">
-        <f>data!$B$78</f>
+        <f>data!$B$77</f>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="21" t="str">
-        <f>data!$B$30</f>
+        <f>data!$B$32</f>
       </c>
       <c r="B106" s="21"/>
       <c r="C106" s="21"/>
@@ -8283,10 +8283,10 @@
       <c r="E106" s="21"/>
       <c r="F106" s="21"/>
       <c r="G106" s="21" t="str">
-        <f>data!$B$32</f>
+        <f>data!$B$30</f>
       </c>
       <c r="I106" s="21" t="str">
-        <f>data!$B$77</f>
+        <f>data!$B$79</f>
       </c>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
@@ -8294,12 +8294,12 @@
       <c r="M106" s="21"/>
       <c r="N106" s="21"/>
       <c r="O106" s="21" t="str">
-        <f>data!$B$79</f>
+        <f>data!$B$77</f>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="21" t="str">
-        <f>data!$B$31</f>
+        <f>data!$B$32</f>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="21"/>
@@ -8307,10 +8307,10 @@
       <c r="E107" s="21"/>
       <c r="F107" s="21"/>
       <c r="G107" s="21" t="str">
-        <f>data!$B$32</f>
+        <f>data!$B$31</f>
       </c>
       <c r="I107" s="21" t="str">
-        <f>data!$B$78</f>
+        <f>data!$B$79</f>
       </c>
       <c r="J107" s="21"/>
       <c r="K107" s="21"/>
@@ -8318,7 +8318,7 @@
       <c r="M107" s="21"/>
       <c r="N107" s="21"/>
       <c r="O107" s="21" t="str">
-        <f>data!$B$79</f>
+        <f>data!$B$78</f>
       </c>
     </row>
     <row r="109">
@@ -8372,28 +8372,28 @@
       <c r="O114" s="20"/>
     </row>
     <row r="115">
-      <c r="A115" s="23" t="s">
+      <c r="A115" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D115" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G115" s="24" t="s">
+      <c r="G115" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I115" s="23" t="s">
+      <c r="I115" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L115" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O115" s="24" t="s">
+      <c r="O115" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="21" t="str">
-        <f>data!$B$33</f>
+        <f>data!$B$34</f>
       </c>
       <c r="B116" s="21"/>
       <c r="C116" s="21"/>
@@ -8401,10 +8401,10 @@
       <c r="E116" s="21"/>
       <c r="F116" s="21"/>
       <c r="G116" s="21" t="str">
-        <f>data!$B$34</f>
+        <f>data!$B$33</f>
       </c>
       <c r="I116" s="21" t="str">
-        <f>data!$B$80</f>
+        <f>data!$B$81</f>
       </c>
       <c r="J116" s="21"/>
       <c r="K116" s="21"/>
@@ -8412,12 +8412,12 @@
       <c r="M116" s="21"/>
       <c r="N116" s="21"/>
       <c r="O116" s="21" t="str">
-        <f>data!$B$81</f>
+        <f>data!$B$80</f>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="21" t="str">
-        <f>data!$B$33</f>
+        <f>data!$B$35</f>
       </c>
       <c r="B117" s="21"/>
       <c r="C117" s="21"/>
@@ -8425,10 +8425,10 @@
       <c r="E117" s="21"/>
       <c r="F117" s="21"/>
       <c r="G117" s="21" t="str">
-        <f>data!$B$35</f>
+        <f>data!$B$33</f>
       </c>
       <c r="I117" s="21" t="str">
-        <f>data!$B$80</f>
+        <f>data!$B$82</f>
       </c>
       <c r="J117" s="21"/>
       <c r="K117" s="21"/>
@@ -8436,12 +8436,12 @@
       <c r="M117" s="21"/>
       <c r="N117" s="21"/>
       <c r="O117" s="21" t="str">
-        <f>data!$B$82</f>
+        <f>data!$B$80</f>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="21" t="str">
-        <f>data!$B$34</f>
+        <f>data!$B$35</f>
       </c>
       <c r="B118" s="21"/>
       <c r="C118" s="21"/>
@@ -8449,10 +8449,10 @@
       <c r="E118" s="21"/>
       <c r="F118" s="21"/>
       <c r="G118" s="21" t="str">
-        <f>data!$B$35</f>
+        <f>data!$B$34</f>
       </c>
       <c r="I118" s="21" t="str">
-        <f>data!$B$81</f>
+        <f>data!$B$82</f>
       </c>
       <c r="J118" s="21"/>
       <c r="K118" s="21"/>
@@ -8460,7 +8460,7 @@
       <c r="M118" s="21"/>
       <c r="N118" s="21"/>
       <c r="O118" s="21" t="str">
-        <f>data!$B$82</f>
+        <f>data!$B$81</f>
       </c>
     </row>
     <row r="120">
@@ -8514,28 +8514,28 @@
       <c r="O125" s="20"/>
     </row>
     <row r="126">
-      <c r="A126" s="23" t="s">
+      <c r="A126" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D126" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G126" s="24" t="s">
+      <c r="G126" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I126" s="23" t="s">
+      <c r="I126" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L126" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O126" s="24" t="s">
+      <c r="O126" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="21" t="str">
-        <f>data!$B$36</f>
+        <f>data!$B$37</f>
       </c>
       <c r="B127" s="21"/>
       <c r="C127" s="21"/>
@@ -8543,10 +8543,10 @@
       <c r="E127" s="21"/>
       <c r="F127" s="21"/>
       <c r="G127" s="21" t="str">
-        <f>data!$B$37</f>
+        <f>data!$B$36</f>
       </c>
       <c r="I127" s="21" t="str">
-        <f>data!$B$83</f>
+        <f>data!$B$84</f>
       </c>
       <c r="J127" s="21"/>
       <c r="K127" s="21"/>
@@ -8554,12 +8554,12 @@
       <c r="M127" s="21"/>
       <c r="N127" s="21"/>
       <c r="O127" s="21" t="str">
-        <f>data!$B$84</f>
+        <f>data!$B$83</f>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="21" t="str">
-        <f>data!$B$36</f>
+        <f>data!$B$38</f>
       </c>
       <c r="B128" s="21"/>
       <c r="C128" s="21"/>
@@ -8567,10 +8567,10 @@
       <c r="E128" s="21"/>
       <c r="F128" s="21"/>
       <c r="G128" s="21" t="str">
-        <f>data!$B$38</f>
+        <f>data!$B$36</f>
       </c>
       <c r="I128" s="21" t="str">
-        <f>data!$B$83</f>
+        <f>data!$B$85</f>
       </c>
       <c r="J128" s="21"/>
       <c r="K128" s="21"/>
@@ -8578,12 +8578,12 @@
       <c r="M128" s="21"/>
       <c r="N128" s="21"/>
       <c r="O128" s="21" t="str">
-        <f>data!$B$85</f>
+        <f>data!$B$83</f>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="21" t="str">
-        <f>data!$B$37</f>
+        <f>data!$B$38</f>
       </c>
       <c r="B129" s="21"/>
       <c r="C129" s="21"/>
@@ -8591,10 +8591,10 @@
       <c r="E129" s="21"/>
       <c r="F129" s="21"/>
       <c r="G129" s="21" t="str">
-        <f>data!$B$38</f>
+        <f>data!$B$37</f>
       </c>
       <c r="I129" s="21" t="str">
-        <f>data!$B$84</f>
+        <f>data!$B$85</f>
       </c>
       <c r="J129" s="21"/>
       <c r="K129" s="21"/>
@@ -8602,7 +8602,7 @@
       <c r="M129" s="21"/>
       <c r="N129" s="21"/>
       <c r="O129" s="21" t="str">
-        <f>data!$B$85</f>
+        <f>data!$B$84</f>
       </c>
     </row>
     <row r="131">
@@ -8656,28 +8656,28 @@
       <c r="O136" s="20"/>
     </row>
     <row r="137">
-      <c r="A137" s="23" t="s">
+      <c r="A137" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D137" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G137" s="24" t="s">
+      <c r="G137" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I137" s="23" t="s">
+      <c r="I137" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L137" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O137" s="24" t="s">
+      <c r="O137" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="21" t="str">
-        <f>data!$B$39</f>
+        <f>data!$B$40</f>
       </c>
       <c r="B138" s="21"/>
       <c r="C138" s="21"/>
@@ -8685,10 +8685,10 @@
       <c r="E138" s="21"/>
       <c r="F138" s="21"/>
       <c r="G138" s="21" t="str">
-        <f>data!$B$40</f>
+        <f>data!$B$39</f>
       </c>
       <c r="I138" s="21" t="str">
-        <f>data!$B$86</f>
+        <f>data!$B$87</f>
       </c>
       <c r="J138" s="21"/>
       <c r="K138" s="21"/>
@@ -8696,12 +8696,12 @@
       <c r="M138" s="21"/>
       <c r="N138" s="21"/>
       <c r="O138" s="21" t="str">
-        <f>data!$B$87</f>
+        <f>data!$B$86</f>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="21" t="str">
-        <f>data!$B$39</f>
+        <f>data!$B$41</f>
       </c>
       <c r="B139" s="21"/>
       <c r="C139" s="21"/>
@@ -8709,10 +8709,10 @@
       <c r="E139" s="21"/>
       <c r="F139" s="21"/>
       <c r="G139" s="21" t="str">
-        <f>data!$B$41</f>
+        <f>data!$B$39</f>
       </c>
       <c r="I139" s="21" t="str">
-        <f>data!$B$86</f>
+        <f>data!$B$88</f>
       </c>
       <c r="J139" s="21"/>
       <c r="K139" s="21"/>
@@ -8720,12 +8720,12 @@
       <c r="M139" s="21"/>
       <c r="N139" s="21"/>
       <c r="O139" s="21" t="str">
-        <f>data!$B$88</f>
+        <f>data!$B$86</f>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="21" t="str">
-        <f>data!$B$40</f>
+        <f>data!$B$41</f>
       </c>
       <c r="B140" s="21"/>
       <c r="C140" s="21"/>
@@ -8733,10 +8733,10 @@
       <c r="E140" s="21"/>
       <c r="F140" s="21"/>
       <c r="G140" s="21" t="str">
-        <f>data!$B$41</f>
+        <f>data!$B$40</f>
       </c>
       <c r="I140" s="21" t="str">
-        <f>data!$B$87</f>
+        <f>data!$B$88</f>
       </c>
       <c r="J140" s="21"/>
       <c r="K140" s="21"/>
@@ -8744,7 +8744,7 @@
       <c r="M140" s="21"/>
       <c r="N140" s="21"/>
       <c r="O140" s="21" t="str">
-        <f>data!$B$88</f>
+        <f>data!$B$87</f>
       </c>
     </row>
     <row r="142">
@@ -8798,28 +8798,28 @@
       <c r="O147" s="20"/>
     </row>
     <row r="148">
-      <c r="A148" s="23" t="s">
+      <c r="A148" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D148" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G148" s="24" t="s">
+      <c r="G148" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I148" s="23" t="s">
+      <c r="I148" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L148" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O148" s="24" t="s">
+      <c r="O148" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="21" t="str">
-        <f>data!$B$42</f>
+        <f>data!$B$43</f>
       </c>
       <c r="B149" s="21"/>
       <c r="C149" s="21"/>
@@ -8827,10 +8827,10 @@
       <c r="E149" s="21"/>
       <c r="F149" s="21"/>
       <c r="G149" s="21" t="str">
-        <f>data!$B$43</f>
+        <f>data!$B$42</f>
       </c>
       <c r="I149" s="21" t="str">
-        <f>data!$B$89</f>
+        <f>data!$B$90</f>
       </c>
       <c r="J149" s="21"/>
       <c r="K149" s="21"/>
@@ -8838,12 +8838,12 @@
       <c r="M149" s="21"/>
       <c r="N149" s="21"/>
       <c r="O149" s="21" t="str">
-        <f>data!$B$90</f>
+        <f>data!$B$89</f>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="21" t="str">
-        <f>data!$B$42</f>
+        <f>data!$B$44</f>
       </c>
       <c r="B150" s="21"/>
       <c r="C150" s="21"/>
@@ -8851,10 +8851,10 @@
       <c r="E150" s="21"/>
       <c r="F150" s="21"/>
       <c r="G150" s="21" t="str">
-        <f>data!$B$44</f>
+        <f>data!$B$42</f>
       </c>
       <c r="I150" s="21" t="str">
-        <f>data!$B$89</f>
+        <f>data!$B$91</f>
       </c>
       <c r="J150" s="21"/>
       <c r="K150" s="21"/>
@@ -8862,12 +8862,12 @@
       <c r="M150" s="21"/>
       <c r="N150" s="21"/>
       <c r="O150" s="21" t="str">
-        <f>data!$B$91</f>
+        <f>data!$B$89</f>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="21" t="str">
-        <f>data!$B$43</f>
+        <f>data!$B$44</f>
       </c>
       <c r="B151" s="21"/>
       <c r="C151" s="21"/>
@@ -8875,10 +8875,10 @@
       <c r="E151" s="21"/>
       <c r="F151" s="21"/>
       <c r="G151" s="21" t="str">
-        <f>data!$B$44</f>
+        <f>data!$B$43</f>
       </c>
       <c r="I151" s="21" t="str">
-        <f>data!$B$90</f>
+        <f>data!$B$91</f>
       </c>
       <c r="J151" s="21"/>
       <c r="K151" s="21"/>
@@ -8886,7 +8886,7 @@
       <c r="M151" s="21"/>
       <c r="N151" s="21"/>
       <c r="O151" s="21" t="str">
-        <f>data!$B$91</f>
+        <f>data!$B$90</f>
       </c>
     </row>
     <row r="153">
@@ -8940,28 +8940,28 @@
       <c r="O158" s="20"/>
     </row>
     <row r="159">
-      <c r="A159" s="23" t="s">
+      <c r="A159" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D159" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G159" s="24" t="s">
+      <c r="G159" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I159" s="23" t="s">
+      <c r="I159" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L159" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O159" s="24" t="s">
+      <c r="O159" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="21" t="str">
-        <f>data!$B$45</f>
+        <f>data!$B$46</f>
       </c>
       <c r="B160" s="21"/>
       <c r="C160" s="21"/>
@@ -8969,10 +8969,10 @@
       <c r="E160" s="21"/>
       <c r="F160" s="21"/>
       <c r="G160" s="21" t="str">
-        <f>data!$B$46</f>
+        <f>data!$B$45</f>
       </c>
       <c r="I160" s="21" t="str">
-        <f>data!$B$92</f>
+        <f>data!$B$93</f>
       </c>
       <c r="J160" s="21"/>
       <c r="K160" s="21"/>
@@ -8980,12 +8980,12 @@
       <c r="M160" s="21"/>
       <c r="N160" s="21"/>
       <c r="O160" s="21" t="str">
-        <f>data!$B$93</f>
+        <f>data!$B$92</f>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="21" t="str">
-        <f>data!$B$45</f>
+        <f>data!$B$47</f>
       </c>
       <c r="B161" s="21"/>
       <c r="C161" s="21"/>
@@ -8993,12 +8993,12 @@
       <c r="E161" s="21"/>
       <c r="F161" s="21"/>
       <c r="G161" s="21" t="str">
-        <f>data!$B$47</f>
+        <f>data!$B$45</f>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="21" t="str">
-        <f>data!$B$46</f>
+        <f>data!$B$47</f>
       </c>
       <c r="B162" s="21"/>
       <c r="C162" s="21"/>
@@ -9006,7 +9006,7 @@
       <c r="E162" s="21"/>
       <c r="F162" s="21"/>
       <c r="G162" s="21" t="str">
-        <f>data!$B$47</f>
+        <f>data!$B$46</f>
       </c>
     </row>
     <row r="164">
@@ -9047,19 +9047,19 @@
       <c r="G169" s="20"/>
     </row>
     <row r="170">
-      <c r="A170" s="23" t="s">
+      <c r="A170" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D170" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G170" s="24" t="s">
+      <c r="G170" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="21" t="str">
-        <f>data!$B$48</f>
+        <f>data!$B$49</f>
       </c>
       <c r="B171" s="21"/>
       <c r="C171" s="21"/>
@@ -9067,7 +9067,7 @@
       <c r="E171" s="21"/>
       <c r="F171" s="21"/>
       <c r="G171" s="21" t="str">
-        <f>data!$B$49</f>
+        <f>data!$B$48</f>
       </c>
     </row>
     <row r="173">
@@ -9193,28 +9193,28 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L4" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -9222,10 +9222,10 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
       </c>
       <c r="I5" s="21" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G54)</f>
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -9233,7 +9233,7 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G54)</f>
       </c>
     </row>
     <row r="7">
@@ -9277,28 +9277,28 @@
       <c r="O11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L12" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O12" s="24" t="s">
+      <c r="O12" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G76)</f>
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!G66)</f>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -9306,10 +9306,10 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G76)</f>
       </c>
       <c r="I13" s="21" t="str">
-        <f>CONCATENATE("Pool I.1 ",'Pool Matches'!G98)</f>
+        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!G88)</f>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -9317,7 +9317,7 @@
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
       <c r="O13" s="21" t="str">
-        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!G88)</f>
+        <f>CONCATENATE("Pool I.1 ",'Pool Matches'!G98)</f>
       </c>
     </row>
     <row r="15">
@@ -9361,28 +9361,28 @@
       <c r="O19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L20" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O20" s="24" t="s">
+      <c r="O20" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="str">
-        <f>CONCATENATE("Pool K.1 ",'Pool Matches'!G120)</f>
+        <f>CONCATENATE("Pool J.2 ",'Pool Matches'!G110)</f>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -9390,10 +9390,10 @@
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21" t="str">
-        <f>CONCATENATE("Pool J.2 ",'Pool Matches'!G110)</f>
+        <f>CONCATENATE("Pool K.1 ",'Pool Matches'!G120)</f>
       </c>
       <c r="I21" s="21" t="str">
-        <f>CONCATENATE("Pool M.1 ",'Pool Matches'!G142)</f>
+        <f>CONCATENATE("Pool L.2 ",'Pool Matches'!G132)</f>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
@@ -9401,7 +9401,7 @@
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
       <c r="O21" s="21" t="str">
-        <f>CONCATENATE("Pool L.2 ",'Pool Matches'!G132)</f>
+        <f>CONCATENATE("Pool M.1 ",'Pool Matches'!G142)</f>
       </c>
     </row>
     <row r="23">
@@ -9445,28 +9445,28 @@
       <c r="O27" s="20"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I28" s="23" t="s">
+      <c r="I28" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L28" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O28" s="24" t="s">
+      <c r="O28" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="str">
-        <f>CONCATENATE("Pool O.1 ",'Pool Matches'!G164)</f>
+        <f>CONCATENATE("Pool N.2 ",'Pool Matches'!G154)</f>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -9474,10 +9474,10 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21" t="str">
-        <f>CONCATENATE("Pool N.2 ",'Pool Matches'!G154)</f>
+        <f>CONCATENATE("Pool O.1 ",'Pool Matches'!G164)</f>
       </c>
       <c r="I29" s="21" t="str">
-        <f>CONCATENATE("Pool Q.1 ",'Pool Matches'!O10)</f>
+        <f>CONCATENATE("Pool P.2 ",'Pool Matches'!G174)</f>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
@@ -9485,7 +9485,7 @@
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21" t="str">
-        <f>CONCATENATE("Pool P.2 ",'Pool Matches'!G174)</f>
+        <f>CONCATENATE("Pool Q.1 ",'Pool Matches'!O10)</f>
       </c>
     </row>
     <row r="31">
@@ -9529,28 +9529,28 @@
       <c r="O35" s="20"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G36" s="24" t="s">
+      <c r="G36" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L36" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O36" s="24" t="s">
+      <c r="O36" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="str">
-        <f>CONCATENATE("Pool S.1 ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool R.2 ",'Pool Matches'!O22)</f>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -9558,10 +9558,10 @@
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21" t="str">
-        <f>CONCATENATE("Pool R.2 ",'Pool Matches'!O22)</f>
+        <f>CONCATENATE("Pool S.1 ",'Pool Matches'!O32)</f>
       </c>
       <c r="I37" s="21" t="str">
-        <f>CONCATENATE("Pool U.1 ",'Pool Matches'!O54)</f>
+        <f>CONCATENATE("Pool T.2 ",'Pool Matches'!O44)</f>
       </c>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
@@ -9569,7 +9569,7 @@
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
       <c r="O37" s="21" t="str">
-        <f>CONCATENATE("Pool T.2 ",'Pool Matches'!O44)</f>
+        <f>CONCATENATE("Pool U.1 ",'Pool Matches'!O54)</f>
       </c>
     </row>
     <row r="39">
@@ -9613,28 +9613,28 @@
       <c r="O43" s="20"/>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D44" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L44" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O44" s="24" t="s">
+      <c r="O44" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
-        <f>CONCATENATE("Pool W.1 ",'Pool Matches'!O76)</f>
+        <f>CONCATENATE("Pool V.2 ",'Pool Matches'!O66)</f>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -9642,10 +9642,10 @@
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21" t="str">
-        <f>CONCATENATE("Pool V.2 ",'Pool Matches'!O66)</f>
+        <f>CONCATENATE("Pool W.1 ",'Pool Matches'!O76)</f>
       </c>
       <c r="I45" s="21" t="str">
-        <f>CONCATENATE("Pool Y.1 ",'Pool Matches'!O98)</f>
+        <f>CONCATENATE("Pool X.2 ",'Pool Matches'!O88)</f>
       </c>
       <c r="J45" s="21"/>
       <c r="K45" s="21"/>
@@ -9653,7 +9653,7 @@
       <c r="M45" s="21"/>
       <c r="N45" s="21"/>
       <c r="O45" s="21" t="str">
-        <f>CONCATENATE("Pool X.2 ",'Pool Matches'!O88)</f>
+        <f>CONCATENATE("Pool Y.1 ",'Pool Matches'!O98)</f>
       </c>
     </row>
     <row r="47">
@@ -9697,28 +9697,28 @@
       <c r="O51" s="20"/>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D52" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="G52" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I52" s="23" t="s">
+      <c r="I52" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L52" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O52" s="24" t="s">
+      <c r="O52" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="str">
-        <f>CONCATENATE("Pool AA.1 ",'Pool Matches'!O120)</f>
+        <f>CONCATENATE("Pool Z.2 ",'Pool Matches'!O110)</f>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -9726,10 +9726,10 @@
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
       <c r="G53" s="21" t="str">
-        <f>CONCATENATE("Pool Z.2 ",'Pool Matches'!O110)</f>
+        <f>CONCATENATE("Pool AA.1 ",'Pool Matches'!O120)</f>
       </c>
       <c r="I53" s="21" t="str">
-        <f>CONCATENATE("Pool CC.1 ",'Pool Matches'!O142)</f>
+        <f>CONCATENATE("Pool BB.2 ",'Pool Matches'!O132)</f>
       </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
@@ -9737,7 +9737,7 @@
       <c r="M53" s="21"/>
       <c r="N53" s="21"/>
       <c r="O53" s="21" t="str">
-        <f>CONCATENATE("Pool BB.2 ",'Pool Matches'!O132)</f>
+        <f>CONCATENATE("Pool CC.1 ",'Pool Matches'!O142)</f>
       </c>
     </row>
     <row r="55">
@@ -9781,28 +9781,28 @@
       <c r="O59" s="20"/>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G60" s="24" t="s">
+      <c r="G60" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I60" s="23" t="s">
+      <c r="I60" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L60" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O60" s="24" t="s">
+      <c r="O60" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="str">
-        <f>CONCATENATE("Pool EE.1 ",'Pool Matches'!O164)</f>
+        <f>CONCATENATE("Pool DD.2 ",'Pool Matches'!O154)</f>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -9810,10 +9810,10 @@
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
       <c r="G61" s="21" t="str">
-        <f>CONCATENATE("Pool DD.2 ",'Pool Matches'!O154)</f>
+        <f>CONCATENATE("Pool EE.1 ",'Pool Matches'!O164)</f>
       </c>
       <c r="I61" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
       </c>
       <c r="J61" s="21"/>
       <c r="K61" s="21"/>
@@ -9821,7 +9821,7 @@
       <c r="M61" s="21"/>
       <c r="N61" s="21"/>
       <c r="O61" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
       </c>
     </row>
     <row r="63">
@@ -9865,28 +9865,28 @@
       <c r="O67" s="20"/>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G68" s="24" t="s">
+      <c r="G68" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L68" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O68" s="24" t="s">
+      <c r="O68" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G55)</f>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
@@ -9894,10 +9894,10 @@
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
       <c r="G69" s="21" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
       </c>
       <c r="I69" s="21" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!G65)</f>
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G77)</f>
       </c>
       <c r="J69" s="21"/>
       <c r="K69" s="21"/>
@@ -9905,7 +9905,7 @@
       <c r="M69" s="21"/>
       <c r="N69" s="21"/>
       <c r="O69" s="21" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G77)</f>
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!G65)</f>
       </c>
     </row>
     <row r="71">
@@ -9949,28 +9949,28 @@
       <c r="O75" s="20"/>
     </row>
     <row r="76">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D76" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G76" s="24" t="s">
+      <c r="G76" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I76" s="23" t="s">
+      <c r="I76" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L76" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O76" s="24" t="s">
+      <c r="O76" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="21" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool I.2 ",'Pool Matches'!G99)</f>
       </c>
       <c r="B77" s="21"/>
       <c r="C77" s="21"/>
@@ -9978,10 +9978,10 @@
       <c r="E77" s="21"/>
       <c r="F77" s="21"/>
       <c r="G77" s="21" t="str">
-        <f>CONCATENATE("Pool I.2 ",'Pool Matches'!G99)</f>
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!G87)</f>
       </c>
       <c r="I77" s="21" t="str">
-        <f>CONCATENATE("Pool J.1 ",'Pool Matches'!G109)</f>
+        <f>CONCATENATE("Pool K.2 ",'Pool Matches'!G121)</f>
       </c>
       <c r="J77" s="21"/>
       <c r="K77" s="21"/>
@@ -9989,7 +9989,7 @@
       <c r="M77" s="21"/>
       <c r="N77" s="21"/>
       <c r="O77" s="21" t="str">
-        <f>CONCATENATE("Pool K.2 ",'Pool Matches'!G121)</f>
+        <f>CONCATENATE("Pool J.1 ",'Pool Matches'!G109)</f>
       </c>
     </row>
     <row r="79">
@@ -10033,28 +10033,28 @@
       <c r="O83" s="20"/>
     </row>
     <row r="84">
-      <c r="A84" s="23" t="s">
+      <c r="A84" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D84" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G84" s="24" t="s">
+      <c r="G84" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I84" s="23" t="s">
+      <c r="I84" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L84" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O84" s="24" t="s">
+      <c r="O84" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="21" t="str">
-        <f>CONCATENATE("Pool L.1 ",'Pool Matches'!G131)</f>
+        <f>CONCATENATE("Pool M.2 ",'Pool Matches'!G143)</f>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="21"/>
@@ -10062,10 +10062,10 @@
       <c r="E85" s="21"/>
       <c r="F85" s="21"/>
       <c r="G85" s="21" t="str">
-        <f>CONCATENATE("Pool M.2 ",'Pool Matches'!G143)</f>
+        <f>CONCATENATE("Pool L.1 ",'Pool Matches'!G131)</f>
       </c>
       <c r="I85" s="21" t="str">
-        <f>CONCATENATE("Pool N.1 ",'Pool Matches'!G153)</f>
+        <f>CONCATENATE("Pool O.2 ",'Pool Matches'!G165)</f>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -10073,7 +10073,7 @@
       <c r="M85" s="21"/>
       <c r="N85" s="21"/>
       <c r="O85" s="21" t="str">
-        <f>CONCATENATE("Pool O.2 ",'Pool Matches'!G165)</f>
+        <f>CONCATENATE("Pool N.1 ",'Pool Matches'!G153)</f>
       </c>
     </row>
     <row r="87">
@@ -10117,28 +10117,28 @@
       <c r="O91" s="20"/>
     </row>
     <row r="92">
-      <c r="A92" s="23" t="s">
+      <c r="A92" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D92" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="24" t="s">
+      <c r="G92" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I92" s="23" t="s">
+      <c r="I92" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L92" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O92" s="24" t="s">
+      <c r="O92" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="21" t="str">
-        <f>CONCATENATE("Pool P.1 ",'Pool Matches'!G173)</f>
+        <f>CONCATENATE("Pool Q.2 ",'Pool Matches'!O11)</f>
       </c>
       <c r="B93" s="21"/>
       <c r="C93" s="21"/>
@@ -10146,10 +10146,10 @@
       <c r="E93" s="21"/>
       <c r="F93" s="21"/>
       <c r="G93" s="21" t="str">
-        <f>CONCATENATE("Pool Q.2 ",'Pool Matches'!O11)</f>
+        <f>CONCATENATE("Pool P.1 ",'Pool Matches'!G173)</f>
       </c>
       <c r="I93" s="21" t="str">
-        <f>CONCATENATE("Pool R.1 ",'Pool Matches'!O21)</f>
+        <f>CONCATENATE("Pool S.2 ",'Pool Matches'!O33)</f>
       </c>
       <c r="J93" s="21"/>
       <c r="K93" s="21"/>
@@ -10157,7 +10157,7 @@
       <c r="M93" s="21"/>
       <c r="N93" s="21"/>
       <c r="O93" s="21" t="str">
-        <f>CONCATENATE("Pool S.2 ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool R.1 ",'Pool Matches'!O21)</f>
       </c>
     </row>
     <row r="95">
@@ -10201,28 +10201,28 @@
       <c r="O99" s="20"/>
     </row>
     <row r="100">
-      <c r="A100" s="23" t="s">
+      <c r="A100" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D100" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G100" s="24" t="s">
+      <c r="G100" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I100" s="23" t="s">
+      <c r="I100" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L100" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O100" s="24" t="s">
+      <c r="O100" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="21" t="str">
-        <f>CONCATENATE("Pool T.1 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool U.2 ",'Pool Matches'!O55)</f>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="21"/>
@@ -10230,10 +10230,10 @@
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
       <c r="G101" s="21" t="str">
-        <f>CONCATENATE("Pool U.2 ",'Pool Matches'!O55)</f>
+        <f>CONCATENATE("Pool T.1 ",'Pool Matches'!O43)</f>
       </c>
       <c r="I101" s="21" t="str">
-        <f>CONCATENATE("Pool V.1 ",'Pool Matches'!O65)</f>
+        <f>CONCATENATE("Pool W.2 ",'Pool Matches'!O77)</f>
       </c>
       <c r="J101" s="21"/>
       <c r="K101" s="21"/>
@@ -10241,7 +10241,7 @@
       <c r="M101" s="21"/>
       <c r="N101" s="21"/>
       <c r="O101" s="21" t="str">
-        <f>CONCATENATE("Pool W.2 ",'Pool Matches'!O77)</f>
+        <f>CONCATENATE("Pool V.1 ",'Pool Matches'!O65)</f>
       </c>
     </row>
     <row r="103">
@@ -10285,28 +10285,28 @@
       <c r="O107" s="20"/>
     </row>
     <row r="108">
-      <c r="A108" s="23" t="s">
+      <c r="A108" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D108" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G108" s="24" t="s">
+      <c r="G108" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I108" s="23" t="s">
+      <c r="I108" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L108" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O108" s="24" t="s">
+      <c r="O108" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="21" t="str">
-        <f>CONCATENATE("Pool X.1 ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool Y.2 ",'Pool Matches'!O99)</f>
       </c>
       <c r="B109" s="21"/>
       <c r="C109" s="21"/>
@@ -10314,10 +10314,10 @@
       <c r="E109" s="21"/>
       <c r="F109" s="21"/>
       <c r="G109" s="21" t="str">
-        <f>CONCATENATE("Pool Y.2 ",'Pool Matches'!O99)</f>
+        <f>CONCATENATE("Pool X.1 ",'Pool Matches'!O87)</f>
       </c>
       <c r="I109" s="21" t="str">
-        <f>CONCATENATE("Pool Z.1 ",'Pool Matches'!O109)</f>
+        <f>CONCATENATE("Pool AA.2 ",'Pool Matches'!O121)</f>
       </c>
       <c r="J109" s="21"/>
       <c r="K109" s="21"/>
@@ -10325,7 +10325,7 @@
       <c r="M109" s="21"/>
       <c r="N109" s="21"/>
       <c r="O109" s="21" t="str">
-        <f>CONCATENATE("Pool AA.2 ",'Pool Matches'!O121)</f>
+        <f>CONCATENATE("Pool Z.1 ",'Pool Matches'!O109)</f>
       </c>
     </row>
     <row r="111">
@@ -10369,28 +10369,28 @@
       <c r="O115" s="20"/>
     </row>
     <row r="116">
-      <c r="A116" s="23" t="s">
+      <c r="A116" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D116" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G116" s="24" t="s">
+      <c r="G116" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I116" s="23" t="s">
+      <c r="I116" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L116" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O116" s="24" t="s">
+      <c r="O116" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="21" t="str">
-        <f>CONCATENATE("Pool BB.1 ",'Pool Matches'!O131)</f>
+        <f>CONCATENATE("Pool CC.2 ",'Pool Matches'!O143)</f>
       </c>
       <c r="B117" s="21"/>
       <c r="C117" s="21"/>
@@ -10398,10 +10398,10 @@
       <c r="E117" s="21"/>
       <c r="F117" s="21"/>
       <c r="G117" s="21" t="str">
-        <f>CONCATENATE("Pool CC.2 ",'Pool Matches'!O143)</f>
+        <f>CONCATENATE("Pool BB.1 ",'Pool Matches'!O131)</f>
       </c>
       <c r="I117" s="21" t="str">
-        <f>CONCATENATE("Pool DD.1 ",'Pool Matches'!O153)</f>
+        <f>CONCATENATE("Pool EE.2 ",'Pool Matches'!O165)</f>
       </c>
       <c r="J117" s="21"/>
       <c r="K117" s="21"/>
@@ -10409,7 +10409,7 @@
       <c r="M117" s="21"/>
       <c r="N117" s="21"/>
       <c r="O117" s="21" t="str">
-        <f>CONCATENATE("Pool EE.2 ",'Pool Matches'!O165)</f>
+        <f>CONCATENATE("Pool DD.1 ",'Pool Matches'!O153)</f>
       </c>
     </row>
     <row r="119">
@@ -10472,28 +10472,28 @@
       <c r="O130" s="20"/>
     </row>
     <row r="131">
-      <c r="A131" s="23" t="s">
+      <c r="A131" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D131" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G131" s="24" t="s">
+      <c r="G131" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I131" s="23" t="s">
+      <c r="I131" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L131" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O131" s="24" t="s">
+      <c r="O131" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
       </c>
       <c r="B132" s="21"/>
       <c r="C132" s="21"/>
@@ -10501,10 +10501,10 @@
       <c r="E132" s="21"/>
       <c r="F132" s="21"/>
       <c r="G132" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
       </c>
       <c r="I132" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="J132" s="21"/>
       <c r="K132" s="21"/>
@@ -10512,7 +10512,7 @@
       <c r="M132" s="21"/>
       <c r="N132" s="21"/>
       <c r="O132" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
       </c>
     </row>
     <row r="134">
@@ -10556,28 +10556,28 @@
       <c r="O138" s="20"/>
     </row>
     <row r="139">
-      <c r="A139" s="23" t="s">
+      <c r="A139" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D139" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G139" s="24" t="s">
+      <c r="G139" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I139" s="23" t="s">
+      <c r="I139" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L139" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O139" s="24" t="s">
+      <c r="O139" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
       </c>
       <c r="B140" s="21"/>
       <c r="C140" s="21"/>
@@ -10585,10 +10585,10 @@
       <c r="E140" s="21"/>
       <c r="F140" s="21"/>
       <c r="G140" s="21" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="I140" s="21" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
       </c>
       <c r="J140" s="21"/>
       <c r="K140" s="21"/>
@@ -10596,7 +10596,7 @@
       <c r="M140" s="21"/>
       <c r="N140" s="21"/>
       <c r="O140" s="21" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
       </c>
     </row>
     <row r="142">
@@ -10640,28 +10640,28 @@
       <c r="O146" s="20"/>
     </row>
     <row r="147">
-      <c r="A147" s="23" t="s">
+      <c r="A147" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D147" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G147" s="24" t="s">
+      <c r="G147" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I147" s="23" t="s">
+      <c r="I147" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L147" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O147" s="24" t="s">
+      <c r="O147" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="21" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
+        <f>CONCATENATE("M 9 ",'Elimination Matches'!G39)</f>
       </c>
       <c r="B148" s="21"/>
       <c r="C148" s="21"/>
@@ -10669,10 +10669,10 @@
       <c r="E148" s="21"/>
       <c r="F148" s="21"/>
       <c r="G148" s="21" t="str">
-        <f>CONCATENATE("M 9 ",'Elimination Matches'!G39)</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
       </c>
       <c r="I148" s="21" t="str">
-        <f>CONCATENATE("M 10 ",'Elimination Matches'!O39)</f>
+        <f>CONCATENATE("M 11 ",'Elimination Matches'!G47)</f>
       </c>
       <c r="J148" s="21"/>
       <c r="K148" s="21"/>
@@ -10680,7 +10680,7 @@
       <c r="M148" s="21"/>
       <c r="N148" s="21"/>
       <c r="O148" s="21" t="str">
-        <f>CONCATENATE("M 11 ",'Elimination Matches'!G47)</f>
+        <f>CONCATENATE("M 10 ",'Elimination Matches'!O39)</f>
       </c>
     </row>
     <row r="150">
@@ -10724,28 +10724,28 @@
       <c r="O154" s="20"/>
     </row>
     <row r="155">
-      <c r="A155" s="23" t="s">
+      <c r="A155" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D155" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G155" s="24" t="s">
+      <c r="G155" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I155" s="23" t="s">
+      <c r="I155" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L155" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O155" s="24" t="s">
+      <c r="O155" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="21" t="str">
-        <f>CONCATENATE("M 12 ",'Elimination Matches'!O47)</f>
+        <f>CONCATENATE("M 13 ",'Elimination Matches'!G55)</f>
       </c>
       <c r="B156" s="21"/>
       <c r="C156" s="21"/>
@@ -10753,10 +10753,10 @@
       <c r="E156" s="21"/>
       <c r="F156" s="21"/>
       <c r="G156" s="21" t="str">
-        <f>CONCATENATE("M 13 ",'Elimination Matches'!G55)</f>
+        <f>CONCATENATE("M 12 ",'Elimination Matches'!O47)</f>
       </c>
       <c r="I156" s="21" t="str">
-        <f>CONCATENATE("M 14 ",'Elimination Matches'!O55)</f>
+        <f>CONCATENATE("M 15 ",'Elimination Matches'!G63)</f>
       </c>
       <c r="J156" s="21"/>
       <c r="K156" s="21"/>
@@ -10764,7 +10764,7 @@
       <c r="M156" s="21"/>
       <c r="N156" s="21"/>
       <c r="O156" s="21" t="str">
-        <f>CONCATENATE("M 15 ",'Elimination Matches'!G63)</f>
+        <f>CONCATENATE("M 14 ",'Elimination Matches'!O55)</f>
       </c>
     </row>
     <row r="158">
@@ -10808,28 +10808,28 @@
       <c r="O162" s="20"/>
     </row>
     <row r="163">
-      <c r="A163" s="23" t="s">
+      <c r="A163" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D163" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G163" s="24" t="s">
+      <c r="G163" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I163" s="23" t="s">
+      <c r="I163" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L163" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O163" s="24" t="s">
+      <c r="O163" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
+        <f>CONCATENATE("M 16 ",'Elimination Matches'!O63)</f>
       </c>
       <c r="B164" s="21"/>
       <c r="C164" s="21"/>
@@ -10837,10 +10837,10 @@
       <c r="E164" s="21"/>
       <c r="F164" s="21"/>
       <c r="G164" s="21" t="str">
-        <f>CONCATENATE("M 16 ",'Elimination Matches'!O63)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
       </c>
       <c r="I164" s="21" t="str">
-        <f>CONCATENATE("M 17 ",'Elimination Matches'!G71)</f>
+        <f>CONCATENATE("M 18 ",'Elimination Matches'!O71)</f>
       </c>
       <c r="J164" s="21"/>
       <c r="K164" s="21"/>
@@ -10848,7 +10848,7 @@
       <c r="M164" s="21"/>
       <c r="N164" s="21"/>
       <c r="O164" s="21" t="str">
-        <f>CONCATENATE("M 18 ",'Elimination Matches'!O71)</f>
+        <f>CONCATENATE("M 17 ",'Elimination Matches'!G71)</f>
       </c>
     </row>
     <row r="166">
@@ -10892,28 +10892,28 @@
       <c r="O170" s="20"/>
     </row>
     <row r="171">
-      <c r="A171" s="23" t="s">
+      <c r="A171" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D171" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G171" s="24" t="s">
+      <c r="G171" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I171" s="23" t="s">
+      <c r="I171" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L171" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O171" s="24" t="s">
+      <c r="O171" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="21" t="str">
-        <f>CONCATENATE("M 19 ",'Elimination Matches'!G79)</f>
+        <f>CONCATENATE("M 20 ",'Elimination Matches'!O79)</f>
       </c>
       <c r="B172" s="21"/>
       <c r="C172" s="21"/>
@@ -10921,10 +10921,10 @@
       <c r="E172" s="21"/>
       <c r="F172" s="21"/>
       <c r="G172" s="21" t="str">
-        <f>CONCATENATE("M 20 ",'Elimination Matches'!O79)</f>
+        <f>CONCATENATE("M 19 ",'Elimination Matches'!G79)</f>
       </c>
       <c r="I172" s="21" t="str">
-        <f>CONCATENATE("M 21 ",'Elimination Matches'!G87)</f>
+        <f>CONCATENATE("M 22 ",'Elimination Matches'!O87)</f>
       </c>
       <c r="J172" s="21"/>
       <c r="K172" s="21"/>
@@ -10932,7 +10932,7 @@
       <c r="M172" s="21"/>
       <c r="N172" s="21"/>
       <c r="O172" s="21" t="str">
-        <f>CONCATENATE("M 22 ",'Elimination Matches'!O87)</f>
+        <f>CONCATENATE("M 21 ",'Elimination Matches'!G87)</f>
       </c>
     </row>
     <row r="174">
@@ -10976,28 +10976,28 @@
       <c r="O178" s="20"/>
     </row>
     <row r="179">
-      <c r="A179" s="23" t="s">
+      <c r="A179" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D179" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G179" s="24" t="s">
+      <c r="G179" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I179" s="23" t="s">
+      <c r="I179" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L179" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O179" s="24" t="s">
+      <c r="O179" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="21" t="str">
-        <f>CONCATENATE("M 23 ",'Elimination Matches'!G95)</f>
+        <f>CONCATENATE("M 24 ",'Elimination Matches'!O95)</f>
       </c>
       <c r="B180" s="21"/>
       <c r="C180" s="21"/>
@@ -11005,10 +11005,10 @@
       <c r="E180" s="21"/>
       <c r="F180" s="21"/>
       <c r="G180" s="21" t="str">
-        <f>CONCATENATE("M 24 ",'Elimination Matches'!O95)</f>
+        <f>CONCATENATE("M 23 ",'Elimination Matches'!G95)</f>
       </c>
       <c r="I180" s="21" t="str">
-        <f>CONCATENATE("M 25 ",'Elimination Matches'!G103)</f>
+        <f>CONCATENATE("M 26 ",'Elimination Matches'!O103)</f>
       </c>
       <c r="J180" s="21"/>
       <c r="K180" s="21"/>
@@ -11016,7 +11016,7 @@
       <c r="M180" s="21"/>
       <c r="N180" s="21"/>
       <c r="O180" s="21" t="str">
-        <f>CONCATENATE("M 26 ",'Elimination Matches'!O103)</f>
+        <f>CONCATENATE("M 25 ",'Elimination Matches'!G103)</f>
       </c>
     </row>
     <row r="182">
@@ -11060,28 +11060,28 @@
       <c r="O186" s="20"/>
     </row>
     <row r="187">
-      <c r="A187" s="23" t="s">
+      <c r="A187" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D187" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G187" s="24" t="s">
+      <c r="G187" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I187" s="23" t="s">
+      <c r="I187" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L187" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O187" s="24" t="s">
+      <c r="O187" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="21" t="str">
-        <f>CONCATENATE("M 27 ",'Elimination Matches'!G111)</f>
+        <f>CONCATENATE("M 28 ",'Elimination Matches'!O111)</f>
       </c>
       <c r="B188" s="21"/>
       <c r="C188" s="21"/>
@@ -11089,10 +11089,10 @@
       <c r="E188" s="21"/>
       <c r="F188" s="21"/>
       <c r="G188" s="21" t="str">
-        <f>CONCATENATE("M 28 ",'Elimination Matches'!O111)</f>
+        <f>CONCATENATE("M 27 ",'Elimination Matches'!G111)</f>
       </c>
       <c r="I188" s="21" t="str">
-        <f>CONCATENATE("M 29 ",'Elimination Matches'!G119)</f>
+        <f>CONCATENATE("M 30 ",'Elimination Matches'!O119)</f>
       </c>
       <c r="J188" s="21"/>
       <c r="K188" s="21"/>
@@ -11100,7 +11100,7 @@
       <c r="M188" s="21"/>
       <c r="N188" s="21"/>
       <c r="O188" s="21" t="str">
-        <f>CONCATENATE("M 30 ",'Elimination Matches'!O119)</f>
+        <f>CONCATENATE("M 29 ",'Elimination Matches'!G119)</f>
       </c>
     </row>
     <row r="190">
@@ -11163,28 +11163,28 @@
       <c r="O201" s="20"/>
     </row>
     <row r="202">
-      <c r="A202" s="23" t="s">
+      <c r="A202" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D202" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G202" s="24" t="s">
+      <c r="G202" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I202" s="23" t="s">
+      <c r="I202" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L202" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O202" s="24" t="s">
+      <c r="O202" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="21" t="str">
-        <f>CONCATENATE("M 31 ",'Elimination Matches'!G134)</f>
+        <f>CONCATENATE("M 32 ",'Elimination Matches'!O134)</f>
       </c>
       <c r="B203" s="21"/>
       <c r="C203" s="21"/>
@@ -11192,10 +11192,10 @@
       <c r="E203" s="21"/>
       <c r="F203" s="21"/>
       <c r="G203" s="21" t="str">
-        <f>CONCATENATE("M 32 ",'Elimination Matches'!O134)</f>
+        <f>CONCATENATE("M 31 ",'Elimination Matches'!G134)</f>
       </c>
       <c r="I203" s="21" t="str">
-        <f>CONCATENATE("M 33 ",'Elimination Matches'!G142)</f>
+        <f>CONCATENATE("M 34 ",'Elimination Matches'!O142)</f>
       </c>
       <c r="J203" s="21"/>
       <c r="K203" s="21"/>
@@ -11203,7 +11203,7 @@
       <c r="M203" s="21"/>
       <c r="N203" s="21"/>
       <c r="O203" s="21" t="str">
-        <f>CONCATENATE("M 34 ",'Elimination Matches'!O142)</f>
+        <f>CONCATENATE("M 33 ",'Elimination Matches'!G142)</f>
       </c>
     </row>
     <row r="205">
@@ -11247,28 +11247,28 @@
       <c r="O209" s="20"/>
     </row>
     <row r="210">
-      <c r="A210" s="23" t="s">
+      <c r="A210" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D210" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G210" s="24" t="s">
+      <c r="G210" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I210" s="23" t="s">
+      <c r="I210" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L210" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O210" s="24" t="s">
+      <c r="O210" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="21" t="str">
-        <f>CONCATENATE("M 35 ",'Elimination Matches'!G150)</f>
+        <f>CONCATENATE("M 36 ",'Elimination Matches'!O150)</f>
       </c>
       <c r="B211" s="21"/>
       <c r="C211" s="21"/>
@@ -11276,10 +11276,10 @@
       <c r="E211" s="21"/>
       <c r="F211" s="21"/>
       <c r="G211" s="21" t="str">
-        <f>CONCATENATE("M 36 ",'Elimination Matches'!O150)</f>
+        <f>CONCATENATE("M 35 ",'Elimination Matches'!G150)</f>
       </c>
       <c r="I211" s="21" t="str">
-        <f>CONCATENATE("M 37 ",'Elimination Matches'!G158)</f>
+        <f>CONCATENATE("M 38 ",'Elimination Matches'!O158)</f>
       </c>
       <c r="J211" s="21"/>
       <c r="K211" s="21"/>
@@ -11287,7 +11287,7 @@
       <c r="M211" s="21"/>
       <c r="N211" s="21"/>
       <c r="O211" s="21" t="str">
-        <f>CONCATENATE("M 38 ",'Elimination Matches'!O158)</f>
+        <f>CONCATENATE("M 37 ",'Elimination Matches'!G158)</f>
       </c>
     </row>
     <row r="213">
@@ -11331,28 +11331,28 @@
       <c r="O217" s="20"/>
     </row>
     <row r="218">
-      <c r="A218" s="23" t="s">
+      <c r="A218" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D218" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G218" s="24" t="s">
+      <c r="G218" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I218" s="23" t="s">
+      <c r="I218" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L218" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O218" s="24" t="s">
+      <c r="O218" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="21" t="str">
-        <f>CONCATENATE("M 39 ",'Elimination Matches'!G166)</f>
+        <f>CONCATENATE("M 40 ",'Elimination Matches'!O166)</f>
       </c>
       <c r="B219" s="21"/>
       <c r="C219" s="21"/>
@@ -11360,10 +11360,10 @@
       <c r="E219" s="21"/>
       <c r="F219" s="21"/>
       <c r="G219" s="21" t="str">
-        <f>CONCATENATE("M 40 ",'Elimination Matches'!O166)</f>
+        <f>CONCATENATE("M 39 ",'Elimination Matches'!G166)</f>
       </c>
       <c r="I219" s="21" t="str">
-        <f>CONCATENATE("M 41 ",'Elimination Matches'!G174)</f>
+        <f>CONCATENATE("M 42 ",'Elimination Matches'!O174)</f>
       </c>
       <c r="J219" s="21"/>
       <c r="K219" s="21"/>
@@ -11371,7 +11371,7 @@
       <c r="M219" s="21"/>
       <c r="N219" s="21"/>
       <c r="O219" s="21" t="str">
-        <f>CONCATENATE("M 42 ",'Elimination Matches'!O174)</f>
+        <f>CONCATENATE("M 41 ",'Elimination Matches'!G174)</f>
       </c>
     </row>
     <row r="221">
@@ -11415,28 +11415,28 @@
       <c r="O225" s="20"/>
     </row>
     <row r="226">
-      <c r="A226" s="23" t="s">
+      <c r="A226" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D226" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G226" s="24" t="s">
+      <c r="G226" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I226" s="23" t="s">
+      <c r="I226" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L226" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O226" s="24" t="s">
+      <c r="O226" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="21" t="str">
-        <f>CONCATENATE("M 43 ",'Elimination Matches'!G182)</f>
+        <f>CONCATENATE("M 44 ",'Elimination Matches'!O182)</f>
       </c>
       <c r="B227" s="21"/>
       <c r="C227" s="21"/>
@@ -11444,10 +11444,10 @@
       <c r="E227" s="21"/>
       <c r="F227" s="21"/>
       <c r="G227" s="21" t="str">
-        <f>CONCATENATE("M 44 ",'Elimination Matches'!O182)</f>
+        <f>CONCATENATE("M 43 ",'Elimination Matches'!G182)</f>
       </c>
       <c r="I227" s="21" t="str">
-        <f>CONCATENATE("M 45 ",'Elimination Matches'!G190)</f>
+        <f>CONCATENATE("M 46 ",'Elimination Matches'!O190)</f>
       </c>
       <c r="J227" s="21"/>
       <c r="K227" s="21"/>
@@ -11455,7 +11455,7 @@
       <c r="M227" s="21"/>
       <c r="N227" s="21"/>
       <c r="O227" s="21" t="str">
-        <f>CONCATENATE("M 46 ",'Elimination Matches'!O190)</f>
+        <f>CONCATENATE("M 45 ",'Elimination Matches'!G190)</f>
       </c>
     </row>
     <row r="229">
@@ -11518,28 +11518,28 @@
       <c r="O240" s="20"/>
     </row>
     <row r="241">
-      <c r="A241" s="23" t="s">
+      <c r="A241" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D241" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G241" s="24" t="s">
+      <c r="G241" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I241" s="23" t="s">
+      <c r="I241" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L241" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O241" s="24" t="s">
+      <c r="O241" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="21" t="str">
-        <f>CONCATENATE("M 47 ",'Elimination Matches'!G205)</f>
+        <f>CONCATENATE("M 48 ",'Elimination Matches'!O205)</f>
       </c>
       <c r="B242" s="21"/>
       <c r="C242" s="21"/>
@@ -11547,10 +11547,10 @@
       <c r="E242" s="21"/>
       <c r="F242" s="21"/>
       <c r="G242" s="21" t="str">
-        <f>CONCATENATE("M 48 ",'Elimination Matches'!O205)</f>
+        <f>CONCATENATE("M 47 ",'Elimination Matches'!G205)</f>
       </c>
       <c r="I242" s="21" t="str">
-        <f>CONCATENATE("M 49 ",'Elimination Matches'!G213)</f>
+        <f>CONCATENATE("M 50 ",'Elimination Matches'!O213)</f>
       </c>
       <c r="J242" s="21"/>
       <c r="K242" s="21"/>
@@ -11558,7 +11558,7 @@
       <c r="M242" s="21"/>
       <c r="N242" s="21"/>
       <c r="O242" s="21" t="str">
-        <f>CONCATENATE("M 50 ",'Elimination Matches'!O213)</f>
+        <f>CONCATENATE("M 49 ",'Elimination Matches'!G213)</f>
       </c>
     </row>
     <row r="244">
@@ -11602,28 +11602,28 @@
       <c r="O248" s="20"/>
     </row>
     <row r="249">
-      <c r="A249" s="23" t="s">
+      <c r="A249" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D249" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G249" s="24" t="s">
+      <c r="G249" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I249" s="23" t="s">
+      <c r="I249" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L249" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O249" s="24" t="s">
+      <c r="O249" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="21" t="str">
-        <f>CONCATENATE("M 51 ",'Elimination Matches'!G221)</f>
+        <f>CONCATENATE("M 52 ",'Elimination Matches'!O221)</f>
       </c>
       <c r="B250" s="21"/>
       <c r="C250" s="21"/>
@@ -11631,10 +11631,10 @@
       <c r="E250" s="21"/>
       <c r="F250" s="21"/>
       <c r="G250" s="21" t="str">
-        <f>CONCATENATE("M 52 ",'Elimination Matches'!O221)</f>
+        <f>CONCATENATE("M 51 ",'Elimination Matches'!G221)</f>
       </c>
       <c r="I250" s="21" t="str">
-        <f>CONCATENATE("M 53 ",'Elimination Matches'!G229)</f>
+        <f>CONCATENATE("M 54 ",'Elimination Matches'!O229)</f>
       </c>
       <c r="J250" s="21"/>
       <c r="K250" s="21"/>
@@ -11642,7 +11642,7 @@
       <c r="M250" s="21"/>
       <c r="N250" s="21"/>
       <c r="O250" s="21" t="str">
-        <f>CONCATENATE("M 54 ",'Elimination Matches'!O229)</f>
+        <f>CONCATENATE("M 53 ",'Elimination Matches'!G229)</f>
       </c>
     </row>
     <row r="252">
@@ -11705,28 +11705,28 @@
       <c r="O263" s="20"/>
     </row>
     <row r="264">
-      <c r="A264" s="23" t="s">
+      <c r="A264" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D264" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G264" s="24" t="s">
+      <c r="G264" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="I264" s="23" t="s">
+      <c r="I264" s="24" t="s">
         <v>240</v>
       </c>
       <c r="L264" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O264" s="24" t="s">
+      <c r="O264" s="23" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="21" t="str">
-        <f>CONCATENATE("M 55 ",'Elimination Matches'!G244)</f>
+        <f>CONCATENATE("M 56 ",'Elimination Matches'!O244)</f>
       </c>
       <c r="B265" s="21"/>
       <c r="C265" s="21"/>
@@ -11734,10 +11734,10 @@
       <c r="E265" s="21"/>
       <c r="F265" s="21"/>
       <c r="G265" s="21" t="str">
-        <f>CONCATENATE("M 56 ",'Elimination Matches'!O244)</f>
+        <f>CONCATENATE("M 55 ",'Elimination Matches'!G244)</f>
       </c>
       <c r="I265" s="21" t="str">
-        <f>CONCATENATE("M 57 ",'Elimination Matches'!G252)</f>
+        <f>CONCATENATE("M 58 ",'Elimination Matches'!O252)</f>
       </c>
       <c r="J265" s="21"/>
       <c r="K265" s="21"/>
@@ -11745,7 +11745,7 @@
       <c r="M265" s="21"/>
       <c r="N265" s="21"/>
       <c r="O265" s="21" t="str">
-        <f>CONCATENATE("M 58 ",'Elimination Matches'!O252)</f>
+        <f>CONCATENATE("M 57 ",'Elimination Matches'!G252)</f>
       </c>
     </row>
     <row r="267">
@@ -11799,13 +11799,13 @@
       <c r="G278" s="20"/>
     </row>
     <row r="279">
-      <c r="A279" s="23" t="s">
+      <c r="A279" s="24" t="s">
         <v>240</v>
       </c>
       <c r="D279" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="G279" s="24" t="s">
+      <c r="G279" s="23" t="s">
         <v>242</v>
       </c>
     </row>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -1822,11 +1822,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3129,7 +3133,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3137,7 +3142,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3522,7 +3527,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -11409,7 +11414,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -11794,7 +11799,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,17 +12,19 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
     <sheet name="Tree 3" sheetId="10" r:id="rId13"/>
     <sheet name="Tree 4" sheetId="11" r:id="rId14"/>
-    <sheet name="Tags" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print A" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print B" sheetId="13" r:id="rId16"/>
+    <sheet name="Tags" sheetId="14" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$71</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$158</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$91</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$47</definedName>
+    <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$44</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$279</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <si>
     <t>Number of pools</t>
   </si>
@@ -1220,10 +1222,13 @@
     <t>Round 4 - Match 58</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 6 - Match 0</t>
+    <t>Round 5 - Match 59</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 60</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 61</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -3893,6 +3898,797 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D27</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D28</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D29</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D30</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D31</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D32</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D33</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D34</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D35</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D36</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D37</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D38</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D39</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D40</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D41</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D42</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D43</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D44</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D45</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D46</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B45" s="27" t="str">
+        <f>data!D47</f>
+      </c>
+    </row>
+    <row r="46" ht="270" customHeight="true">
+      <c r="A46" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B46" s="27" t="str">
+        <f>data!D48</f>
+      </c>
+    </row>
+    <row r="47" ht="270" customHeight="true">
+      <c r="A47" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B47" s="27" t="str">
+        <f>data!D49</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D50</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D51</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D52</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D53</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D54</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D55</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D56</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D57</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D58</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D59</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D60</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D61</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D62</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D63</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D64</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D65</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D66</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D67</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D68</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D69</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D70</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D71</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D72</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D73</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D74</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D75</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D76</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D77</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D78</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D79</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D80</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D81</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D82</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D83</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D84</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D85</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D86</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D87</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D88</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D89</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D90</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D91</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D92</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D93</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="14" manualBreakCount="14">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -5106,7 +5902,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -5117,7 +5913,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -5127,7 +5923,7 @@
     </row>
     <row r="15">
       <c r="E15" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
@@ -5137,7 +5933,7 @@
     </row>
     <row r="16">
       <c r="E16" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
@@ -5147,7 +5943,7 @@
     </row>
     <row r="17">
       <c r="E17" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -5157,7 +5953,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -5167,7 +5963,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -10433,7 +11229,7 @@
       <c r="F254" s="13"/>
       <c r="G254" s="13"/>
       <c r="I254" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J254" s="13"/>
       <c r="K254" s="13"/>
@@ -10508,7 +11304,7 @@
     </row>
     <row r="267">
       <c r="A267" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B267" s="13"/>
       <c r="C267" s="13"/>
@@ -10530,7 +11326,7 @@
     </row>
     <row r="269">
       <c r="A269" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O258)</f>
+        <f>CONCATENATE("M 60 ",O258)</f>
       </c>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -10538,7 +11334,7 @@
       <c r="E269" s="14"/>
       <c r="F269" s="14"/>
       <c r="G269" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O258)</f>
+        <f>CONCATENATE("M 59 ",G258)</f>
       </c>
     </row>
     <row r="271">
@@ -10635,781 +11431,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="B16" s="27" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="B25" s="27" t="str">
-        <f>data!D27</f>
-      </c>
-    </row>
-    <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="B26" s="27" t="str">
-        <f>data!D28</f>
-      </c>
-    </row>
-    <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="B27" s="27" t="str">
-        <f>data!D29</f>
-      </c>
-    </row>
-    <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="B28" s="27" t="str">
-        <f>data!D30</f>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="B29" s="27" t="str">
-        <f>data!D31</f>
-      </c>
-    </row>
-    <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="B30" s="27" t="str">
-        <f>data!D32</f>
-      </c>
-    </row>
-    <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="B31" s="27" t="str">
-        <f>data!D33</f>
-      </c>
-    </row>
-    <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="B32" s="27" t="str">
-        <f>data!D34</f>
-      </c>
-    </row>
-    <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B33" s="27" t="str">
-        <f>data!D35</f>
-      </c>
-    </row>
-    <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="B34" s="27" t="str">
-        <f>data!D36</f>
-      </c>
-    </row>
-    <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="B35" s="27" t="str">
-        <f>data!D37</f>
-      </c>
-    </row>
-    <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="B36" s="27" t="str">
-        <f>data!D38</f>
-      </c>
-    </row>
-    <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="B37" s="27" t="str">
-        <f>data!D39</f>
-      </c>
-    </row>
-    <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="B38" s="27" t="str">
-        <f>data!D40</f>
-      </c>
-    </row>
-    <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="B39" s="27" t="str">
-        <f>data!D41</f>
-      </c>
-    </row>
-    <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="B40" s="27" t="str">
-        <f>data!D42</f>
-      </c>
-    </row>
-    <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="B41" s="27" t="str">
-        <f>data!D43</f>
-      </c>
-    </row>
-    <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="B42" s="27" t="str">
-        <f>data!D44</f>
-      </c>
-    </row>
-    <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="B43" s="27" t="str">
-        <f>data!D45</f>
-      </c>
-    </row>
-    <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="B44" s="27" t="str">
-        <f>data!D46</f>
-      </c>
-    </row>
-    <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="B45" s="27" t="str">
-        <f>data!D47</f>
-      </c>
-    </row>
-    <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="B46" s="27" t="str">
-        <f>data!D48</f>
-      </c>
-    </row>
-    <row r="47" ht="270" customHeight="true">
-      <c r="A47" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="B47" s="27" t="str">
-        <f>data!D49</f>
-      </c>
-    </row>
-    <row r="48" ht="270" customHeight="true">
-      <c r="A48" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="B48" s="27" t="str">
-        <f>data!D50</f>
-      </c>
-    </row>
-    <row r="49" ht="270" customHeight="true">
-      <c r="A49" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="B49" s="27" t="str">
-        <f>data!D51</f>
-      </c>
-    </row>
-    <row r="50" ht="270" customHeight="true">
-      <c r="A50" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="B50" s="27" t="str">
-        <f>data!D52</f>
-      </c>
-    </row>
-    <row r="51" ht="270" customHeight="true">
-      <c r="A51" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="B51" s="27" t="str">
-        <f>data!D53</f>
-      </c>
-    </row>
-    <row r="52" ht="270" customHeight="true">
-      <c r="A52" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="B52" s="27" t="str">
-        <f>data!D54</f>
-      </c>
-    </row>
-    <row r="53" ht="270" customHeight="true">
-      <c r="A53" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="B53" s="27" t="str">
-        <f>data!D55</f>
-      </c>
-    </row>
-    <row r="54" ht="270" customHeight="true">
-      <c r="A54" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="B54" s="27" t="str">
-        <f>data!D56</f>
-      </c>
-    </row>
-    <row r="55" ht="270" customHeight="true">
-      <c r="A55" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="B55" s="27" t="str">
-        <f>data!D57</f>
-      </c>
-    </row>
-    <row r="56" ht="270" customHeight="true">
-      <c r="A56" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B56" s="27" t="str">
-        <f>data!D58</f>
-      </c>
-    </row>
-    <row r="57" ht="270" customHeight="true">
-      <c r="A57" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="B57" s="27" t="str">
-        <f>data!D59</f>
-      </c>
-    </row>
-    <row r="58" ht="270" customHeight="true">
-      <c r="A58" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B58" s="27" t="str">
-        <f>data!D60</f>
-      </c>
-    </row>
-    <row r="59" ht="270" customHeight="true">
-      <c r="A59" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="B59" s="27" t="str">
-        <f>data!D61</f>
-      </c>
-    </row>
-    <row r="60" ht="270" customHeight="true">
-      <c r="A60" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="B60" s="27" t="str">
-        <f>data!D62</f>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="true">
-      <c r="A61" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="B61" s="27" t="str">
-        <f>data!D63</f>
-      </c>
-    </row>
-    <row r="62" ht="270" customHeight="true">
-      <c r="A62" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="B62" s="27" t="str">
-        <f>data!D64</f>
-      </c>
-    </row>
-    <row r="63" ht="270" customHeight="true">
-      <c r="A63" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="B63" s="27" t="str">
-        <f>data!D65</f>
-      </c>
-    </row>
-    <row r="64" ht="270" customHeight="true">
-      <c r="A64" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="B64" s="27" t="str">
-        <f>data!D66</f>
-      </c>
-    </row>
-    <row r="65" ht="270" customHeight="true">
-      <c r="A65" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="B65" s="27" t="str">
-        <f>data!D67</f>
-      </c>
-    </row>
-    <row r="66" ht="270" customHeight="true">
-      <c r="A66" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B66" s="27" t="str">
-        <f>data!D68</f>
-      </c>
-    </row>
-    <row r="67" ht="270" customHeight="true">
-      <c r="A67" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="B67" s="27" t="str">
-        <f>data!D69</f>
-      </c>
-    </row>
-    <row r="68" ht="270" customHeight="true">
-      <c r="A68" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B68" s="27" t="str">
-        <f>data!D70</f>
-      </c>
-    </row>
-    <row r="69" ht="270" customHeight="true">
-      <c r="A69" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B69" s="27" t="str">
-        <f>data!D71</f>
-      </c>
-    </row>
-    <row r="70" ht="270" customHeight="true">
-      <c r="A70" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B70" s="27" t="str">
-        <f>data!D72</f>
-      </c>
-    </row>
-    <row r="71" ht="270" customHeight="true">
-      <c r="A71" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="B71" s="27" t="str">
-        <f>data!D73</f>
-      </c>
-    </row>
-    <row r="72" ht="270" customHeight="true">
-      <c r="A72" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="B72" s="27" t="str">
-        <f>data!D74</f>
-      </c>
-    </row>
-    <row r="73" ht="270" customHeight="true">
-      <c r="A73" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B73" s="27" t="str">
-        <f>data!D75</f>
-      </c>
-    </row>
-    <row r="74" ht="270" customHeight="true">
-      <c r="A74" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="B74" s="27" t="str">
-        <f>data!D76</f>
-      </c>
-    </row>
-    <row r="75" ht="270" customHeight="true">
-      <c r="A75" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B75" s="27" t="str">
-        <f>data!D77</f>
-      </c>
-    </row>
-    <row r="76" ht="270" customHeight="true">
-      <c r="A76" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="B76" s="27" t="str">
-        <f>data!D78</f>
-      </c>
-    </row>
-    <row r="77" ht="270" customHeight="true">
-      <c r="A77" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B77" s="27" t="str">
-        <f>data!D79</f>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="true">
-      <c r="A78" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="B78" s="27" t="str">
-        <f>data!D80</f>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="true">
-      <c r="A79" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="B79" s="27" t="str">
-        <f>data!D81</f>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="true">
-      <c r="A80" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="B80" s="27" t="str">
-        <f>data!D82</f>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="true">
-      <c r="A81" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="B81" s="27" t="str">
-        <f>data!D83</f>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="true">
-      <c r="A82" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="B82" s="27" t="str">
-        <f>data!D84</f>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="true">
-      <c r="A83" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="B83" s="27" t="str">
-        <f>data!D85</f>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="true">
-      <c r="A84" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="B84" s="27" t="str">
-        <f>data!D86</f>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="true">
-      <c r="A85" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="B85" s="27" t="str">
-        <f>data!D87</f>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="true">
-      <c r="A86" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B86" s="27" t="str">
-        <f>data!D88</f>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="true">
-      <c r="A87" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B87" s="27" t="str">
-        <f>data!D89</f>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="true">
-      <c r="A88" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="B88" s="27" t="str">
-        <f>data!D90</f>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="true">
-      <c r="A89" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="B89" s="27" t="str">
-        <f>data!D91</f>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="true">
-      <c r="A90" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B90" s="27" t="str">
-        <f>data!D92</f>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="true">
-      <c r="A91" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B91" s="27" t="str">
-        <f>data!D93</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="30" manualBreakCount="30">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-    <brk id="27" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
-    <brk id="33" max="16383" man="true"/>
-    <brk id="36" max="16383" man="true"/>
-    <brk id="39" max="16383" man="true"/>
-    <brk id="42" max="16383" man="true"/>
-    <brk id="45" max="16383" man="true"/>
-    <brk id="48" max="16383" man="true"/>
-    <brk id="51" max="16383" man="true"/>
-    <brk id="54" max="16383" man="true"/>
-    <brk id="57" max="16383" man="true"/>
-    <brk id="60" max="16383" man="true"/>
-    <brk id="63" max="16383" man="true"/>
-    <brk id="66" max="16383" man="true"/>
-    <brk id="69" max="16383" man="true"/>
-    <brk id="72" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
-    <brk id="81" max="16383" man="true"/>
-    <brk id="84" max="16383" man="true"/>
-    <brk id="87" max="16383" man="true"/>
-    <brk id="90" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -3221,7 +3221,7 @@
         <f>"2. " &amp; data!$B$51</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="7">
@@ -3242,7 +3242,7 @@
         <f>'data'!$A$55</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3265,7 +3265,7 @@
         <f>"2. " &amp; data!$B$54</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3282,7 +3282,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3304,7 +3304,7 @@
         <f>"1. " &amp; data!$B$56</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3329,7 +3329,7 @@
         <f>"3. " &amp; data!$B$58</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3349,7 +3349,7 @@
         <f>'data'!$A$61</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3368,7 +3368,7 @@
         <f>"2. " &amp; data!$B$60</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3385,7 +3385,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G152)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3407,7 +3407,7 @@
         <f>"1. " &amp; data!$B$62</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G168)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3432,7 +3432,7 @@
         <f>"3. " &amp; data!$B$64</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G186)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3452,7 +3452,7 @@
         <f>'data'!$A$67</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G202)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3471,7 +3471,7 @@
         <f>"2. " &amp; data!$B$66</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G220)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3492,7 +3492,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G236)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3512,7 +3512,7 @@
         <f>"1. " &amp; data!$B$68</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G254)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3602,7 +3602,7 @@
         <f>"1. " &amp; data!$B$74</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G269)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G267)</f>
       </c>
     </row>
     <row r="6">
@@ -3619,7 +3619,7 @@
         <f>"3. " &amp; data!$B$76</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -3637,7 +3637,7 @@
         <f>'data'!$A$79</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3660,7 +3660,7 @@
         <f>"2. " &amp; data!$B$78</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3677,7 +3677,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3699,7 +3699,7 @@
         <f>"1. " &amp; data!$B$80</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3724,7 +3724,7 @@
         <f>"3. " &amp; data!$B$82</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O103)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3744,7 +3744,7 @@
         <f>'data'!$A$85</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O121)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3763,7 +3763,7 @@
         <f>"2. " &amp; data!$B$84</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O137)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3780,7 +3780,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O155)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O152)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3802,7 +3802,7 @@
         <f>"1. " &amp; data!$B$86</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O171)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O168)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3827,7 +3827,7 @@
         <f>"3. " &amp; data!$B$88</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O189)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O186)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3847,7 +3847,7 @@
         <f>'data'!$A$91</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O205)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3866,7 +3866,7 @@
         <f>"2. " &amp; data!$B$90</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O223)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3887,7 +3887,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O239)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3907,7 +3907,7 @@
         <f>"1. " &amp; data!$B$92</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O255)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -12163,7 +12163,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -12171,10 +12171,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -12182,7 +12182,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
     </row>
     <row r="6">
@@ -12247,7 +12247,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -12255,10 +12255,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -12266,7 +12266,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
     </row>
     <row r="14">
@@ -12331,7 +12331,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -12339,10 +12339,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -12350,7 +12350,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
       </c>
     </row>
     <row r="22">
@@ -12415,7 +12415,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -12423,10 +12423,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G152)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -12434,7 +12434,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
       </c>
     </row>
     <row r="30">
@@ -12499,7 +12499,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G169)</f>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -12507,10 +12507,10 @@
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G185)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G186)</f>
       </c>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
@@ -12518,7 +12518,7 @@
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G168)</f>
       </c>
     </row>
     <row r="38">
@@ -12583,7 +12583,7 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G203)</f>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -12591,10 +12591,10 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G219)</f>
       </c>
       <c r="I44" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G220)</f>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
@@ -12602,7 +12602,7 @@
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
       <c r="O44" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G202)</f>
       </c>
     </row>
     <row r="46">
@@ -12667,7 +12667,7 @@
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G237)</f>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -12675,10 +12675,10 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G253)</f>
       </c>
       <c r="I52" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G254)</f>
       </c>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
@@ -12686,7 +12686,7 @@
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G236)</f>
       </c>
     </row>
     <row r="54">
@@ -12751,7 +12751,7 @@
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G270)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G268)</f>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -12759,10 +12759,10 @@
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
       <c r="G60" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
@@ -12770,7 +12770,7 @@
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
       <c r="O60" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G269)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G267)</f>
       </c>
     </row>
     <row r="62">
@@ -12835,7 +12835,7 @@
     </row>
     <row r="68">
       <c r="A68" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -12843,10 +12843,10 @@
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="G68" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="I68" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
@@ -12854,7 +12854,7 @@
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
       <c r="O68" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="70">
@@ -12919,7 +12919,7 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -12927,10 +12927,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
       </c>
       <c r="I76" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
@@ -12938,7 +12938,7 @@
       <c r="M76" s="18"/>
       <c r="N76" s="18"/>
       <c r="O76" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
       </c>
     </row>
     <row r="78">
@@ -13003,7 +13003,7 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O104)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -13011,10 +13011,10 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O120)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
       </c>
       <c r="I84" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O121)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
       </c>
       <c r="J84" s="18"/>
       <c r="K84" s="18"/>
@@ -13022,7 +13022,7 @@
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O103)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
       </c>
     </row>
     <row r="86">
@@ -13087,7 +13087,7 @@
     </row>
     <row r="92">
       <c r="A92" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O138)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -13095,10 +13095,10 @@
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
       <c r="G92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O154)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
       </c>
       <c r="I92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O155)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O152)</f>
       </c>
       <c r="J92" s="18"/>
       <c r="K92" s="18"/>
@@ -13106,7 +13106,7 @@
       <c r="M92" s="18"/>
       <c r="N92" s="18"/>
       <c r="O92" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O137)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
       </c>
     </row>
     <row r="94">
@@ -13171,7 +13171,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O169)</f>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -13179,10 +13179,10 @@
       <c r="E100" s="18"/>
       <c r="F100" s="18"/>
       <c r="G100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O188)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O185)</f>
       </c>
       <c r="I100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O189)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O186)</f>
       </c>
       <c r="J100" s="18"/>
       <c r="K100" s="18"/>
@@ -13190,7 +13190,7 @@
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O171)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O168)</f>
       </c>
     </row>
     <row r="102">
@@ -13255,7 +13255,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O206)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13263,10 +13263,10 @@
       <c r="E108" s="18"/>
       <c r="F108" s="18"/>
       <c r="G108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O222)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
       </c>
       <c r="I108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O223)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
       </c>
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
@@ -13274,7 +13274,7 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O205)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
       </c>
     </row>
     <row r="110">
@@ -13339,7 +13339,7 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O240)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -13347,10 +13347,10 @@
       <c r="E116" s="18"/>
       <c r="F116" s="18"/>
       <c r="G116" s="14" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O254)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
       </c>
       <c r="I116" s="14" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O255)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
       </c>
       <c r="J116" s="18"/>
       <c r="K116" s="18"/>
@@ -13358,7 +13358,7 @@
       <c r="M116" s="18"/>
       <c r="N116" s="18"/>
       <c r="O116" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O239)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
       </c>
     </row>
     <row r="118">
@@ -13431,7 +13431,7 @@
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
       <c r="G129" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
       <c r="I129" s="14" t="str">
         <f>CONCATENATE("M 16 ",O6)</f>
@@ -13442,7 +13442,7 @@
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
       <c r="O129" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="131">
@@ -14815,7 +14815,7 @@
         <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
     </row>
     <row r="7">
@@ -14836,7 +14836,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -14859,7 +14859,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -14876,7 +14876,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -14898,7 +14898,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -14923,7 +14923,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -14943,7 +14943,7 @@
         <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -14962,7 +14962,7 @@
         <f>"2. " &amp; data!$B$13</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -14979,7 +14979,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15001,7 +15001,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G185)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -15026,7 +15026,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G169)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15046,7 +15046,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G219)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -15065,7 +15065,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G203)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15086,7 +15086,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G253)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -15106,7 +15106,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G237)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -15196,7 +15196,7 @@
         <f>"1. " &amp; data!$B$27</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="6">
@@ -15213,7 +15213,7 @@
         <f>"3. " &amp; data!$B$29</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G270)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G268)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -15231,7 +15231,7 @@
         <f>'data'!$A$32</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -15254,7 +15254,7 @@
         <f>"2. " &amp; data!$B$31</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -15271,7 +15271,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -15293,7 +15293,7 @@
         <f>"1. " &amp; data!$B$33</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -15318,7 +15318,7 @@
         <f>"3. " &amp; data!$B$35</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O120)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -15338,7 +15338,7 @@
         <f>'data'!$A$38</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O104)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -15357,7 +15357,7 @@
         <f>"2. " &amp; data!$B$37</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O154)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -15374,7 +15374,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O138)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15396,7 +15396,7 @@
         <f>"1. " &amp; data!$B$39</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O188)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O185)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -15421,7 +15421,7 @@
         <f>"3. " &amp; data!$B$41</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O169)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15441,7 +15441,7 @@
         <f>'data'!$A$44</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O222)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -15460,7 +15460,7 @@
         <f>"2. " &amp; data!$B$43</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O206)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15481,7 +15481,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O254)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -15501,7 +15501,7 @@
         <f>"1. " &amp; data!$B$45</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O240)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -6776,10 +6776,10 @@
         <f>RANK(AC9,$AC$9:$AC$11)+COUNTIF($AC$8:AC8,AC9)</f>
       </c>
       <c r="U9" t="str">
-        <f>=(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
+        <f>(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
       </c>
       <c r="AC9" t="str">
-        <f>=(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
+        <f>(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
       </c>
     </row>
     <row r="10">
@@ -6826,10 +6826,10 @@
         <f>RANK(AC10,$AC$9:$AC$11)+COUNTIF($AC$8:AC9,AC10)</f>
       </c>
       <c r="U10" t="str">
-        <f>=(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
+        <f>(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
       </c>
       <c r="AC10" t="str">
-        <f>=(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
+        <f>(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
       </c>
     </row>
     <row r="11">
@@ -6876,10 +6876,10 @@
         <f>RANK(AC11,$AC$9:$AC$11)+COUNTIF($AC$8:AC10,AC11)</f>
       </c>
       <c r="U11" t="str">
-        <f>=(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
+        <f>(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
       </c>
       <c r="AC11" t="str">
-        <f>=(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
+        <f>(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
       </c>
     </row>
     <row r="14">
@@ -7134,10 +7134,10 @@
         <f>RANK(AC26,$AC$26:$AC$28)+COUNTIF($AC$25:AC25,AC26)</f>
       </c>
       <c r="U26" t="str">
-        <f>=(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
+        <f>(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
       </c>
       <c r="AC26" t="str">
-        <f>=(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
+        <f>(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
       </c>
     </row>
     <row r="27">
@@ -7184,10 +7184,10 @@
         <f>RANK(AC27,$AC$26:$AC$28)+COUNTIF($AC$25:AC26,AC27)</f>
       </c>
       <c r="U27" t="str">
-        <f>=(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
+        <f>(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
       </c>
       <c r="AC27" t="str">
-        <f>=(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
+        <f>(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
       </c>
     </row>
     <row r="28">
@@ -7234,10 +7234,10 @@
         <f>RANK(AC28,$AC$26:$AC$28)+COUNTIF($AC$25:AC27,AC28)</f>
       </c>
       <c r="U28" t="str">
-        <f>=(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
+        <f>(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
       </c>
       <c r="AC28" t="str">
-        <f>=(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
+        <f>(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
       </c>
     </row>
     <row r="31">
@@ -7492,10 +7492,10 @@
         <f>RANK(AC43,$AC$43:$AC$45)+COUNTIF($AC$42:AC42,AC43)</f>
       </c>
       <c r="U43" t="str">
-        <f>=(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
+        <f>(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
       </c>
       <c r="AC43" t="str">
-        <f>=(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
+        <f>(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
       </c>
     </row>
     <row r="44">
@@ -7542,10 +7542,10 @@
         <f>RANK(AC44,$AC$43:$AC$45)+COUNTIF($AC$42:AC43,AC44)</f>
       </c>
       <c r="U44" t="str">
-        <f>=(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
+        <f>(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
       </c>
       <c r="AC44" t="str">
-        <f>=(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
+        <f>(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
       </c>
     </row>
     <row r="45">
@@ -7592,10 +7592,10 @@
         <f>RANK(AC45,$AC$43:$AC$45)+COUNTIF($AC$42:AC44,AC45)</f>
       </c>
       <c r="U45" t="str">
-        <f>=(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
+        <f>(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
       </c>
       <c r="AC45" t="str">
-        <f>=(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
+        <f>(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
       </c>
     </row>
     <row r="48">
@@ -7850,10 +7850,10 @@
         <f>RANK(AC60,$AC$60:$AC$62)+COUNTIF($AC$59:AC59,AC60)</f>
       </c>
       <c r="U60" t="str">
-        <f>=(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
+        <f>(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
       </c>
       <c r="AC60" t="str">
-        <f>=(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
+        <f>(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="61">
@@ -7900,10 +7900,10 @@
         <f>RANK(AC61,$AC$60:$AC$62)+COUNTIF($AC$59:AC60,AC61)</f>
       </c>
       <c r="U61" t="str">
-        <f>=(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
+        <f>(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
       </c>
       <c r="AC61" t="str">
-        <f>=(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
+        <f>(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
       </c>
     </row>
     <row r="62">
@@ -7950,10 +7950,10 @@
         <f>RANK(AC62,$AC$60:$AC$62)+COUNTIF($AC$59:AC61,AC62)</f>
       </c>
       <c r="U62" t="str">
-        <f>=(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
+        <f>(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
       </c>
       <c r="AC62" t="str">
-        <f>=(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
+        <f>(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
       </c>
     </row>
     <row r="65">
@@ -8208,10 +8208,10 @@
         <f>RANK(AC77,$AC$77:$AC$79)+COUNTIF($AC$76:AC76,AC77)</f>
       </c>
       <c r="U77" t="str">
-        <f>=(B77*1000000)-(C77*10000)+(D77*100)+(E77*1)-(F77*0.01)</f>
+        <f>(B77*1000000)-(C77*10000)+(D77*100)+(E77*1)-(F77*0.01)</f>
       </c>
       <c r="AC77" t="str">
-        <f>=(J77*1000000)-(K77*10000)+(L77*100)+(M77*1)-(N77*0.01)</f>
+        <f>(J77*1000000)-(K77*10000)+(L77*100)+(M77*1)-(N77*0.01)</f>
       </c>
     </row>
     <row r="78">
@@ -8258,10 +8258,10 @@
         <f>RANK(AC78,$AC$77:$AC$79)+COUNTIF($AC$76:AC77,AC78)</f>
       </c>
       <c r="U78" t="str">
-        <f>=(B78*1000000)-(C78*10000)+(D78*100)+(E78*1)-(F78*0.01)</f>
+        <f>(B78*1000000)-(C78*10000)+(D78*100)+(E78*1)-(F78*0.01)</f>
       </c>
       <c r="AC78" t="str">
-        <f>=(J78*1000000)-(K78*10000)+(L78*100)+(M78*1)-(N78*0.01)</f>
+        <f>(J78*1000000)-(K78*10000)+(L78*100)+(M78*1)-(N78*0.01)</f>
       </c>
     </row>
     <row r="79">
@@ -8308,10 +8308,10 @@
         <f>RANK(AC79,$AC$77:$AC$79)+COUNTIF($AC$76:AC78,AC79)</f>
       </c>
       <c r="U79" t="str">
-        <f>=(B79*1000000)-(C79*10000)+(D79*100)+(E79*1)-(F79*0.01)</f>
+        <f>(B79*1000000)-(C79*10000)+(D79*100)+(E79*1)-(F79*0.01)</f>
       </c>
       <c r="AC79" t="str">
-        <f>=(J79*1000000)-(K79*10000)+(L79*100)+(M79*1)-(N79*0.01)</f>
+        <f>(J79*1000000)-(K79*10000)+(L79*100)+(M79*1)-(N79*0.01)</f>
       </c>
     </row>
     <row r="82">
@@ -8566,10 +8566,10 @@
         <f>RANK(AC94,$AC$94:$AC$96)+COUNTIF($AC$93:AC93,AC94)</f>
       </c>
       <c r="U94" t="str">
-        <f>=(B94*1000000)-(C94*10000)+(D94*100)+(E94*1)-(F94*0.01)</f>
+        <f>(B94*1000000)-(C94*10000)+(D94*100)+(E94*1)-(F94*0.01)</f>
       </c>
       <c r="AC94" t="str">
-        <f>=(J94*1000000)-(K94*10000)+(L94*100)+(M94*1)-(N94*0.01)</f>
+        <f>(J94*1000000)-(K94*10000)+(L94*100)+(M94*1)-(N94*0.01)</f>
       </c>
     </row>
     <row r="95">
@@ -8616,10 +8616,10 @@
         <f>RANK(AC95,$AC$94:$AC$96)+COUNTIF($AC$93:AC94,AC95)</f>
       </c>
       <c r="U95" t="str">
-        <f>=(B95*1000000)-(C95*10000)+(D95*100)+(E95*1)-(F95*0.01)</f>
+        <f>(B95*1000000)-(C95*10000)+(D95*100)+(E95*1)-(F95*0.01)</f>
       </c>
       <c r="AC95" t="str">
-        <f>=(J95*1000000)-(K95*10000)+(L95*100)+(M95*1)-(N95*0.01)</f>
+        <f>(J95*1000000)-(K95*10000)+(L95*100)+(M95*1)-(N95*0.01)</f>
       </c>
     </row>
     <row r="96">
@@ -8666,10 +8666,10 @@
         <f>RANK(AC96,$AC$94:$AC$96)+COUNTIF($AC$93:AC95,AC96)</f>
       </c>
       <c r="U96" t="str">
-        <f>=(B96*1000000)-(C96*10000)+(D96*100)+(E96*1)-(F96*0.01)</f>
+        <f>(B96*1000000)-(C96*10000)+(D96*100)+(E96*1)-(F96*0.01)</f>
       </c>
       <c r="AC96" t="str">
-        <f>=(J96*1000000)-(K96*10000)+(L96*100)+(M96*1)-(N96*0.01)</f>
+        <f>(J96*1000000)-(K96*10000)+(L96*100)+(M96*1)-(N96*0.01)</f>
       </c>
     </row>
     <row r="99">
@@ -8924,10 +8924,10 @@
         <f>RANK(AC111,$AC$111:$AC$113)+COUNTIF($AC$110:AC110,AC111)</f>
       </c>
       <c r="U111" t="str">
-        <f>=(B111*1000000)-(C111*10000)+(D111*100)+(E111*1)-(F111*0.01)</f>
+        <f>(B111*1000000)-(C111*10000)+(D111*100)+(E111*1)-(F111*0.01)</f>
       </c>
       <c r="AC111" t="str">
-        <f>=(J111*1000000)-(K111*10000)+(L111*100)+(M111*1)-(N111*0.01)</f>
+        <f>(J111*1000000)-(K111*10000)+(L111*100)+(M111*1)-(N111*0.01)</f>
       </c>
     </row>
     <row r="112">
@@ -8974,10 +8974,10 @@
         <f>RANK(AC112,$AC$111:$AC$113)+COUNTIF($AC$110:AC111,AC112)</f>
       </c>
       <c r="U112" t="str">
-        <f>=(B112*1000000)-(C112*10000)+(D112*100)+(E112*1)-(F112*0.01)</f>
+        <f>(B112*1000000)-(C112*10000)+(D112*100)+(E112*1)-(F112*0.01)</f>
       </c>
       <c r="AC112" t="str">
-        <f>=(J112*1000000)-(K112*10000)+(L112*100)+(M112*1)-(N112*0.01)</f>
+        <f>(J112*1000000)-(K112*10000)+(L112*100)+(M112*1)-(N112*0.01)</f>
       </c>
     </row>
     <row r="113">
@@ -9024,10 +9024,10 @@
         <f>RANK(AC113,$AC$111:$AC$113)+COUNTIF($AC$110:AC112,AC113)</f>
       </c>
       <c r="U113" t="str">
-        <f>=(B113*1000000)-(C113*10000)+(D113*100)+(E113*1)-(F113*0.01)</f>
+        <f>(B113*1000000)-(C113*10000)+(D113*100)+(E113*1)-(F113*0.01)</f>
       </c>
       <c r="AC113" t="str">
-        <f>=(J113*1000000)-(K113*10000)+(L113*100)+(M113*1)-(N113*0.01)</f>
+        <f>(J113*1000000)-(K113*10000)+(L113*100)+(M113*1)-(N113*0.01)</f>
       </c>
     </row>
     <row r="116">
@@ -9282,10 +9282,10 @@
         <f>RANK(AC128,$AC$128:$AC$130)+COUNTIF($AC$127:AC127,AC128)</f>
       </c>
       <c r="U128" t="str">
-        <f>=(B128*1000000)-(C128*10000)+(D128*100)+(E128*1)-(F128*0.01)</f>
+        <f>(B128*1000000)-(C128*10000)+(D128*100)+(E128*1)-(F128*0.01)</f>
       </c>
       <c r="AC128" t="str">
-        <f>=(J128*1000000)-(K128*10000)+(L128*100)+(M128*1)-(N128*0.01)</f>
+        <f>(J128*1000000)-(K128*10000)+(L128*100)+(M128*1)-(N128*0.01)</f>
       </c>
     </row>
     <row r="129">
@@ -9332,10 +9332,10 @@
         <f>RANK(AC129,$AC$128:$AC$130)+COUNTIF($AC$127:AC128,AC129)</f>
       </c>
       <c r="U129" t="str">
-        <f>=(B129*1000000)-(C129*10000)+(D129*100)+(E129*1)-(F129*0.01)</f>
+        <f>(B129*1000000)-(C129*10000)+(D129*100)+(E129*1)-(F129*0.01)</f>
       </c>
       <c r="AC129" t="str">
-        <f>=(J129*1000000)-(K129*10000)+(L129*100)+(M129*1)-(N129*0.01)</f>
+        <f>(J129*1000000)-(K129*10000)+(L129*100)+(M129*1)-(N129*0.01)</f>
       </c>
     </row>
     <row r="130">
@@ -9382,10 +9382,10 @@
         <f>RANK(AC130,$AC$128:$AC$130)+COUNTIF($AC$127:AC129,AC130)</f>
       </c>
       <c r="U130" t="str">
-        <f>=(B130*1000000)-(C130*10000)+(D130*100)+(E130*1)-(F130*0.01)</f>
+        <f>(B130*1000000)-(C130*10000)+(D130*100)+(E130*1)-(F130*0.01)</f>
       </c>
       <c r="AC130" t="str">
-        <f>=(J130*1000000)-(K130*10000)+(L130*100)+(M130*1)-(N130*0.01)</f>
+        <f>(J130*1000000)-(K130*10000)+(L130*100)+(M130*1)-(N130*0.01)</f>
       </c>
     </row>
     <row r="133">
@@ -9640,10 +9640,10 @@
         <f>RANK(AC145,$AC$145:$AC$147)+COUNTIF($AC$144:AC144,AC145)</f>
       </c>
       <c r="U145" t="str">
-        <f>=(B145*1000000)-(C145*10000)+(D145*100)+(E145*1)-(F145*0.01)</f>
+        <f>(B145*1000000)-(C145*10000)+(D145*100)+(E145*1)-(F145*0.01)</f>
       </c>
       <c r="AC145" t="str">
-        <f>=(J145*1000000)-(K145*10000)+(L145*100)+(M145*1)-(N145*0.01)</f>
+        <f>(J145*1000000)-(K145*10000)+(L145*100)+(M145*1)-(N145*0.01)</f>
       </c>
     </row>
     <row r="146">
@@ -9690,10 +9690,10 @@
         <f>RANK(AC146,$AC$145:$AC$147)+COUNTIF($AC$144:AC145,AC146)</f>
       </c>
       <c r="U146" t="str">
-        <f>=(B146*1000000)-(C146*10000)+(D146*100)+(E146*1)-(F146*0.01)</f>
+        <f>(B146*1000000)-(C146*10000)+(D146*100)+(E146*1)-(F146*0.01)</f>
       </c>
       <c r="AC146" t="str">
-        <f>=(J146*1000000)-(K146*10000)+(L146*100)+(M146*1)-(N146*0.01)</f>
+        <f>(J146*1000000)-(K146*10000)+(L146*100)+(M146*1)-(N146*0.01)</f>
       </c>
     </row>
     <row r="147">
@@ -9740,10 +9740,10 @@
         <f>RANK(AC147,$AC$145:$AC$147)+COUNTIF($AC$144:AC146,AC147)</f>
       </c>
       <c r="U147" t="str">
-        <f>=(B147*1000000)-(C147*10000)+(D147*100)+(E147*1)-(F147*0.01)</f>
+        <f>(B147*1000000)-(C147*10000)+(D147*100)+(E147*1)-(F147*0.01)</f>
       </c>
       <c r="AC147" t="str">
-        <f>=(J147*1000000)-(K147*10000)+(L147*100)+(M147*1)-(N147*0.01)</f>
+        <f>(J147*1000000)-(K147*10000)+(L147*100)+(M147*1)-(N147*0.01)</f>
       </c>
     </row>
     <row r="150">
@@ -9998,10 +9998,10 @@
         <f>RANK(AC162,$AC$162:$AC$164)+COUNTIF($AC$161:AC161,AC162)</f>
       </c>
       <c r="U162" t="str">
-        <f>=(B162*1000000)-(C162*10000)+(D162*100)+(E162*1)-(F162*0.01)</f>
+        <f>(B162*1000000)-(C162*10000)+(D162*100)+(E162*1)-(F162*0.01)</f>
       </c>
       <c r="AC162" t="str">
-        <f>=(J162*1000000)-(K162*10000)+(L162*100)+(M162*1)-(N162*0.01)</f>
+        <f>(J162*1000000)-(K162*10000)+(L162*100)+(M162*1)-(N162*0.01)</f>
       </c>
     </row>
     <row r="163">
@@ -10048,10 +10048,10 @@
         <f>RANK(AC163,$AC$162:$AC$164)+COUNTIF($AC$161:AC162,AC163)</f>
       </c>
       <c r="U163" t="str">
-        <f>=(B163*1000000)-(C163*10000)+(D163*100)+(E163*1)-(F163*0.01)</f>
+        <f>(B163*1000000)-(C163*10000)+(D163*100)+(E163*1)-(F163*0.01)</f>
       </c>
       <c r="AC163" t="str">
-        <f>=(J163*1000000)-(K163*10000)+(L163*100)+(M163*1)-(N163*0.01)</f>
+        <f>(J163*1000000)-(K163*10000)+(L163*100)+(M163*1)-(N163*0.01)</f>
       </c>
     </row>
     <row r="164">
@@ -10098,10 +10098,10 @@
         <f>RANK(AC164,$AC$162:$AC$164)+COUNTIF($AC$161:AC163,AC164)</f>
       </c>
       <c r="U164" t="str">
-        <f>=(B164*1000000)-(C164*10000)+(D164*100)+(E164*1)-(F164*0.01)</f>
+        <f>(B164*1000000)-(C164*10000)+(D164*100)+(E164*1)-(F164*0.01)</f>
       </c>
       <c r="AC164" t="str">
-        <f>=(J164*1000000)-(K164*10000)+(L164*100)+(M164*1)-(N164*0.01)</f>
+        <f>(J164*1000000)-(K164*10000)+(L164*100)+(M164*1)-(N164*0.01)</f>
       </c>
     </row>
     <row r="167">
@@ -10356,10 +10356,10 @@
         <f>RANK(AC179,$AC$179:$AC$181)+COUNTIF($AC$178:AC178,AC179)</f>
       </c>
       <c r="U179" t="str">
-        <f>=(B179*1000000)-(C179*10000)+(D179*100)+(E179*1)-(F179*0.01)</f>
+        <f>(B179*1000000)-(C179*10000)+(D179*100)+(E179*1)-(F179*0.01)</f>
       </c>
       <c r="AC179" t="str">
-        <f>=(J179*1000000)-(K179*10000)+(L179*100)+(M179*1)-(N179*0.01)</f>
+        <f>(J179*1000000)-(K179*10000)+(L179*100)+(M179*1)-(N179*0.01)</f>
       </c>
     </row>
     <row r="180">
@@ -10406,10 +10406,10 @@
         <f>RANK(AC180,$AC$179:$AC$181)+COUNTIF($AC$178:AC179,AC180)</f>
       </c>
       <c r="U180" t="str">
-        <f>=(B180*1000000)-(C180*10000)+(D180*100)+(E180*1)-(F180*0.01)</f>
+        <f>(B180*1000000)-(C180*10000)+(D180*100)+(E180*1)-(F180*0.01)</f>
       </c>
       <c r="AC180" t="str">
-        <f>=(J180*1000000)-(K180*10000)+(L180*100)+(M180*1)-(N180*0.01)</f>
+        <f>(J180*1000000)-(K180*10000)+(L180*100)+(M180*1)-(N180*0.01)</f>
       </c>
     </row>
     <row r="181">
@@ -10456,10 +10456,10 @@
         <f>RANK(AC181,$AC$179:$AC$181)+COUNTIF($AC$178:AC180,AC181)</f>
       </c>
       <c r="U181" t="str">
-        <f>=(B181*1000000)-(C181*10000)+(D181*100)+(E181*1)-(F181*0.01)</f>
+        <f>(B181*1000000)-(C181*10000)+(D181*100)+(E181*1)-(F181*0.01)</f>
       </c>
       <c r="AC181" t="str">
-        <f>=(J181*1000000)-(K181*10000)+(L181*100)+(M181*1)-(N181*0.01)</f>
+        <f>(J181*1000000)-(K181*10000)+(L181*100)+(M181*1)-(N181*0.01)</f>
       </c>
     </row>
     <row r="184">
@@ -10714,10 +10714,10 @@
         <f>RANK(AC196,$AC$196:$AC$198)+COUNTIF($AC$195:AC195,AC196)</f>
       </c>
       <c r="U196" t="str">
-        <f>=(B196*1000000)-(C196*10000)+(D196*100)+(E196*1)-(F196*0.01)</f>
+        <f>(B196*1000000)-(C196*10000)+(D196*100)+(E196*1)-(F196*0.01)</f>
       </c>
       <c r="AC196" t="str">
-        <f>=(J196*1000000)-(K196*10000)+(L196*100)+(M196*1)-(N196*0.01)</f>
+        <f>(J196*1000000)-(K196*10000)+(L196*100)+(M196*1)-(N196*0.01)</f>
       </c>
     </row>
     <row r="197">
@@ -10764,10 +10764,10 @@
         <f>RANK(AC197,$AC$196:$AC$198)+COUNTIF($AC$195:AC196,AC197)</f>
       </c>
       <c r="U197" t="str">
-        <f>=(B197*1000000)-(C197*10000)+(D197*100)+(E197*1)-(F197*0.01)</f>
+        <f>(B197*1000000)-(C197*10000)+(D197*100)+(E197*1)-(F197*0.01)</f>
       </c>
       <c r="AC197" t="str">
-        <f>=(J197*1000000)-(K197*10000)+(L197*100)+(M197*1)-(N197*0.01)</f>
+        <f>(J197*1000000)-(K197*10000)+(L197*100)+(M197*1)-(N197*0.01)</f>
       </c>
     </row>
     <row r="198">
@@ -10814,10 +10814,10 @@
         <f>RANK(AC198,$AC$196:$AC$198)+COUNTIF($AC$195:AC197,AC198)</f>
       </c>
       <c r="U198" t="str">
-        <f>=(B198*1000000)-(C198*10000)+(D198*100)+(E198*1)-(F198*0.01)</f>
+        <f>(B198*1000000)-(C198*10000)+(D198*100)+(E198*1)-(F198*0.01)</f>
       </c>
       <c r="AC198" t="str">
-        <f>=(J198*1000000)-(K198*10000)+(L198*100)+(M198*1)-(N198*0.01)</f>
+        <f>(J198*1000000)-(K198*10000)+(L198*100)+(M198*1)-(N198*0.01)</f>
       </c>
     </row>
     <row r="201">
@@ -11072,10 +11072,10 @@
         <f>RANK(AC213,$AC$213:$AC$215)+COUNTIF($AC$212:AC212,AC213)</f>
       </c>
       <c r="U213" t="str">
-        <f>=(B213*1000000)-(C213*10000)+(D213*100)+(E213*1)-(F213*0.01)</f>
+        <f>(B213*1000000)-(C213*10000)+(D213*100)+(E213*1)-(F213*0.01)</f>
       </c>
       <c r="AC213" t="str">
-        <f>=(J213*1000000)-(K213*10000)+(L213*100)+(M213*1)-(N213*0.01)</f>
+        <f>(J213*1000000)-(K213*10000)+(L213*100)+(M213*1)-(N213*0.01)</f>
       </c>
     </row>
     <row r="214">
@@ -11122,10 +11122,10 @@
         <f>RANK(AC214,$AC$213:$AC$215)+COUNTIF($AC$212:AC213,AC214)</f>
       </c>
       <c r="U214" t="str">
-        <f>=(B214*1000000)-(C214*10000)+(D214*100)+(E214*1)-(F214*0.01)</f>
+        <f>(B214*1000000)-(C214*10000)+(D214*100)+(E214*1)-(F214*0.01)</f>
       </c>
       <c r="AC214" t="str">
-        <f>=(J214*1000000)-(K214*10000)+(L214*100)+(M214*1)-(N214*0.01)</f>
+        <f>(J214*1000000)-(K214*10000)+(L214*100)+(M214*1)-(N214*0.01)</f>
       </c>
     </row>
     <row r="215">
@@ -11172,10 +11172,10 @@
         <f>RANK(AC215,$AC$213:$AC$215)+COUNTIF($AC$212:AC214,AC215)</f>
       </c>
       <c r="U215" t="str">
-        <f>=(B215*1000000)-(C215*10000)+(D215*100)+(E215*1)-(F215*0.01)</f>
+        <f>(B215*1000000)-(C215*10000)+(D215*100)+(E215*1)-(F215*0.01)</f>
       </c>
       <c r="AC215" t="str">
-        <f>=(J215*1000000)-(K215*10000)+(L215*100)+(M215*1)-(N215*0.01)</f>
+        <f>(J215*1000000)-(K215*10000)+(L215*100)+(M215*1)-(N215*0.01)</f>
       </c>
     </row>
     <row r="218">
@@ -11430,10 +11430,10 @@
         <f>RANK(AC230,$AC$230:$AC$232)+COUNTIF($AC$229:AC229,AC230)</f>
       </c>
       <c r="U230" t="str">
-        <f>=(B230*1000000)-(C230*10000)+(D230*100)+(E230*1)-(F230*0.01)</f>
+        <f>(B230*1000000)-(C230*10000)+(D230*100)+(E230*1)-(F230*0.01)</f>
       </c>
       <c r="AC230" t="str">
-        <f>=(J230*1000000)-(K230*10000)+(L230*100)+(M230*1)-(N230*0.01)</f>
+        <f>(J230*1000000)-(K230*10000)+(L230*100)+(M230*1)-(N230*0.01)</f>
       </c>
     </row>
     <row r="231">
@@ -11480,10 +11480,10 @@
         <f>RANK(AC231,$AC$230:$AC$232)+COUNTIF($AC$229:AC230,AC231)</f>
       </c>
       <c r="U231" t="str">
-        <f>=(B231*1000000)-(C231*10000)+(D231*100)+(E231*1)-(F231*0.01)</f>
+        <f>(B231*1000000)-(C231*10000)+(D231*100)+(E231*1)-(F231*0.01)</f>
       </c>
       <c r="AC231" t="str">
-        <f>=(J231*1000000)-(K231*10000)+(L231*100)+(M231*1)-(N231*0.01)</f>
+        <f>(J231*1000000)-(K231*10000)+(L231*100)+(M231*1)-(N231*0.01)</f>
       </c>
     </row>
     <row r="232">
@@ -11530,10 +11530,10 @@
         <f>RANK(AC232,$AC$230:$AC$232)+COUNTIF($AC$229:AC231,AC232)</f>
       </c>
       <c r="U232" t="str">
-        <f>=(B232*1000000)-(C232*10000)+(D232*100)+(E232*1)-(F232*0.01)</f>
+        <f>(B232*1000000)-(C232*10000)+(D232*100)+(E232*1)-(F232*0.01)</f>
       </c>
       <c r="AC232" t="str">
-        <f>=(J232*1000000)-(K232*10000)+(L232*100)+(M232*1)-(N232*0.01)</f>
+        <f>(J232*1000000)-(K232*10000)+(L232*100)+(M232*1)-(N232*0.01)</f>
       </c>
     </row>
     <row r="235">
@@ -11766,10 +11766,10 @@
         <f>RANK(AC247,$AC$247:$AC$248)+COUNTIF($AC$246:AC246,AC247)</f>
       </c>
       <c r="U247" t="str">
-        <f>=(B247*1000000)-(C247*10000)+(D247*100)+(E247*1)-(F247*0.01)</f>
+        <f>(B247*1000000)-(C247*10000)+(D247*100)+(E247*1)-(F247*0.01)</f>
       </c>
       <c r="AC247" t="str">
-        <f>=(J247*1000000)-(K247*10000)+(L247*100)+(M247*1)-(N247*0.01)</f>
+        <f>(J247*1000000)-(K247*10000)+(L247*100)+(M247*1)-(N247*0.01)</f>
       </c>
     </row>
     <row r="248">
@@ -11816,10 +11816,10 @@
         <f>RANK(AC248,$AC$247:$AC$248)+COUNTIF($AC$246:AC247,AC248)</f>
       </c>
       <c r="U248" t="str">
-        <f>=(B248*1000000)-(C248*10000)+(D248*100)+(E248*1)-(F248*0.01)</f>
+        <f>(B248*1000000)-(C248*10000)+(D248*100)+(E248*1)-(F248*0.01)</f>
       </c>
       <c r="AC248" t="str">
-        <f>=(J248*1000000)-(K248*10000)+(L248*100)+(M248*1)-(N248*0.01)</f>
+        <f>(J248*1000000)-(K248*10000)+(L248*100)+(M248*1)-(N248*0.01)</f>
       </c>
     </row>
     <row r="249">
@@ -11845,7 +11845,7 @@
         <f>RANK(U249,$U$247:$U$249)+COUNTIF($U$246:U248,U249)</f>
       </c>
       <c r="U249" t="str">
-        <f>=(B249*1000000)-(C249*10000)+(D249*100)+(E249*1)-(F249*0.01)</f>
+        <f>(B249*1000000)-(C249*10000)+(D249*100)+(E249*1)-(F249*0.01)</f>
       </c>
     </row>
     <row r="251">
@@ -11977,7 +11977,7 @@
         <f>RANK(U262,$U$262:$U$263)+COUNTIF($U$261:U261,U262)</f>
       </c>
       <c r="U262" t="str">
-        <f>=(B262*1000000)-(C262*10000)+(D262*100)+(E262*1)-(F262*0.01)</f>
+        <f>(B262*1000000)-(C262*10000)+(D262*100)+(E262*1)-(F262*0.01)</f>
       </c>
     </row>
     <row r="263">
@@ -12003,7 +12003,7 @@
         <f>RANK(U263,$U$262:$U$263)+COUNTIF($U$261:U262,U263)</f>
       </c>
       <c r="U263" t="str">
-        <f>=(B263*1000000)-(C263*10000)+(D263*100)+(E263*1)-(F263*0.01)</f>
+        <f>(B263*1000000)-(C263*10000)+(D263*100)+(E263*1)-(F263*0.01)</f>
       </c>
     </row>
     <row r="266">

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -1367,7 +1367,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4730,912 +4730,912 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
+    <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
+    <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="19" ht="390" customHeight="true">
+    <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="20" ht="390" customHeight="true">
+    <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="21" ht="390" customHeight="true">
+    <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="22" ht="390" customHeight="true">
+    <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="23" ht="390" customHeight="true">
+    <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="24" ht="390" customHeight="true">
+    <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="25" ht="390" customHeight="true">
+    <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="26" ht="390" customHeight="true">
+    <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="27" ht="390" customHeight="true">
+    <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="28" ht="390" customHeight="true">
+    <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" ht="390" customHeight="true">
+    <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="30" ht="390" customHeight="true">
+    <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="31" ht="390" customHeight="true">
+    <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="32" ht="390" customHeight="true">
+    <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="33" ht="390" customHeight="true">
+    <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="34" ht="390" customHeight="true">
+    <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="35" ht="390" customHeight="true">
+    <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="36" ht="390" customHeight="true">
+    <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="37" ht="390" customHeight="true">
+    <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="38" ht="390" customHeight="true">
+    <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="39" ht="390" customHeight="true">
+    <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="40" ht="390" customHeight="true">
+    <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="41" ht="390" customHeight="true">
+    <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="42" ht="390" customHeight="true">
+    <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="43" ht="390" customHeight="true">
+    <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="44" ht="390" customHeight="true">
+    <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="45" ht="390" customHeight="true">
+    <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="46" ht="390" customHeight="true">
+    <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="47" ht="390" customHeight="true">
+    <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="48" ht="390" customHeight="true">
+    <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="49" ht="390" customHeight="true">
+    <row r="49" ht="409" customHeight="true">
       <c r="A49" s="30" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="50" ht="390" customHeight="true">
+    <row r="50" ht="409" customHeight="true">
       <c r="A50" s="30" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="51" ht="390" customHeight="true">
+    <row r="51" ht="409" customHeight="true">
       <c r="A51" s="30" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="52" ht="390" customHeight="true">
+    <row r="52" ht="409" customHeight="true">
       <c r="A52" s="30" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="53" ht="390" customHeight="true">
+    <row r="53" ht="409" customHeight="true">
       <c r="A53" s="30" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="54" ht="390" customHeight="true">
+    <row r="54" ht="409" customHeight="true">
       <c r="A54" s="30" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="55" ht="390" customHeight="true">
+    <row r="55" ht="409" customHeight="true">
       <c r="A55" s="30" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="56" ht="390" customHeight="true">
+    <row r="56" ht="409" customHeight="true">
       <c r="A56" s="30" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="57" ht="390" customHeight="true">
+    <row r="57" ht="409" customHeight="true">
       <c r="A57" s="30" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="58" ht="390" customHeight="true">
+    <row r="58" ht="409" customHeight="true">
       <c r="A58" s="30" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="59" ht="390" customHeight="true">
+    <row r="59" ht="409" customHeight="true">
       <c r="A59" s="30" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="60" ht="390" customHeight="true">
+    <row r="60" ht="409" customHeight="true">
       <c r="A60" s="30" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="61" ht="390" customHeight="true">
+    <row r="61" ht="409" customHeight="true">
       <c r="A61" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="62" ht="390" customHeight="true">
+    <row r="62" ht="409" customHeight="true">
       <c r="A62" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="63" ht="390" customHeight="true">
+    <row r="63" ht="409" customHeight="true">
       <c r="A63" s="30" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="64" ht="390" customHeight="true">
+    <row r="64" ht="409" customHeight="true">
       <c r="A64" s="30" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="65" ht="390" customHeight="true">
+    <row r="65" ht="409" customHeight="true">
       <c r="A65" s="30" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="66" ht="390" customHeight="true">
+    <row r="66" ht="409" customHeight="true">
       <c r="A66" s="30" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="67" ht="390" customHeight="true">
+    <row r="67" ht="409" customHeight="true">
       <c r="A67" s="30" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="68" ht="390" customHeight="true">
+    <row r="68" ht="409" customHeight="true">
       <c r="A68" s="30" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="69" ht="390" customHeight="true">
+    <row r="69" ht="409" customHeight="true">
       <c r="A69" s="30" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="70" ht="390" customHeight="true">
+    <row r="70" ht="409" customHeight="true">
       <c r="A70" s="30" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="71" ht="390" customHeight="true">
+    <row r="71" ht="409" customHeight="true">
       <c r="A71" s="30" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="72" ht="390" customHeight="true">
+    <row r="72" ht="409" customHeight="true">
       <c r="A72" s="30" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="73" ht="390" customHeight="true">
+    <row r="73" ht="409" customHeight="true">
       <c r="A73" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="74" ht="390" customHeight="true">
+    <row r="74" ht="409" customHeight="true">
       <c r="A74" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="75" ht="390" customHeight="true">
+    <row r="75" ht="409" customHeight="true">
       <c r="A75" s="30" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="76" ht="390" customHeight="true">
+    <row r="76" ht="409" customHeight="true">
       <c r="A76" s="30" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="77" ht="390" customHeight="true">
+    <row r="77" ht="409" customHeight="true">
       <c r="A77" s="30" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="78" ht="390" customHeight="true">
+    <row r="78" ht="409" customHeight="true">
       <c r="A78" s="30" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="79" ht="390" customHeight="true">
+    <row r="79" ht="409" customHeight="true">
       <c r="A79" s="30" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="80" ht="390" customHeight="true">
+    <row r="80" ht="409" customHeight="true">
       <c r="A80" s="30" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="81" ht="390" customHeight="true">
+    <row r="81" ht="409" customHeight="true">
       <c r="A81" s="30" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="82" ht="390" customHeight="true">
+    <row r="82" ht="409" customHeight="true">
       <c r="A82" s="30" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="83" ht="390" customHeight="true">
+    <row r="83" ht="409" customHeight="true">
       <c r="A83" s="30" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="84" ht="390" customHeight="true">
+    <row r="84" ht="409" customHeight="true">
       <c r="A84" s="30" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="85" ht="390" customHeight="true">
+    <row r="85" ht="409" customHeight="true">
       <c r="A85" s="30" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="86" ht="390" customHeight="true">
+    <row r="86" ht="409" customHeight="true">
       <c r="A86" s="30" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="87" ht="390" customHeight="true">
+    <row r="87" ht="409" customHeight="true">
       <c r="A87" s="30" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="88" ht="390" customHeight="true">
+    <row r="88" ht="409" customHeight="true">
       <c r="A88" s="30" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="89" ht="390" customHeight="true">
+    <row r="89" ht="409" customHeight="true">
       <c r="A89" s="30" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="90" ht="390" customHeight="true">
+    <row r="90" ht="409" customHeight="true">
       <c r="A90" s="30" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="91" ht="390" customHeight="true">
+    <row r="91" ht="409" customHeight="true">
       <c r="A91" s="30" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="92" ht="390" customHeight="true">
+    <row r="92" ht="409" customHeight="true">
       <c r="A92" s="30" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="93" ht="390" customHeight="true">
+    <row r="93" ht="409" customHeight="true">
       <c r="A93" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="94" ht="390" customHeight="true">
+    <row r="94" ht="409" customHeight="true">
       <c r="A94" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="95" ht="390" customHeight="true">
+    <row r="95" ht="409" customHeight="true">
       <c r="A95" s="30" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="96" ht="390" customHeight="true">
+    <row r="96" ht="409" customHeight="true">
       <c r="A96" s="30" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="97" ht="390" customHeight="true">
+    <row r="97" ht="409" customHeight="true">
       <c r="A97" s="30" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="98" ht="390" customHeight="true">
+    <row r="98" ht="409" customHeight="true">
       <c r="A98" s="30" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="99" ht="390" customHeight="true">
+    <row r="99" ht="409" customHeight="true">
       <c r="A99" s="30" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="100" ht="390" customHeight="true">
+    <row r="100" ht="409" customHeight="true">
       <c r="A100" s="30" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="101" ht="390" customHeight="true">
+    <row r="101" ht="409" customHeight="true">
       <c r="A101" s="30" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="102" ht="390" customHeight="true">
+    <row r="102" ht="409" customHeight="true">
       <c r="A102" s="30" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="103" ht="390" customHeight="true">
+    <row r="103" ht="409" customHeight="true">
       <c r="A103" s="30" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="104" ht="390" customHeight="true">
+    <row r="104" ht="409" customHeight="true">
       <c r="A104" s="30" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="105" ht="390" customHeight="true">
+    <row r="105" ht="409" customHeight="true">
       <c r="A105" s="30" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="106" ht="390" customHeight="true">
+    <row r="106" ht="409" customHeight="true">
       <c r="A106" s="30" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="107" ht="390" customHeight="true">
+    <row r="107" ht="409" customHeight="true">
       <c r="A107" s="30" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="108" ht="390" customHeight="true">
+    <row r="108" ht="409" customHeight="true">
       <c r="A108" s="30" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="109" ht="390" customHeight="true">
+    <row r="109" ht="409" customHeight="true">
       <c r="A109" s="30" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="110" ht="390" customHeight="true">
+    <row r="110" ht="409" customHeight="true">
       <c r="A110" s="30" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="111" ht="390" customHeight="true">
+    <row r="111" ht="409" customHeight="true">
       <c r="A111" s="30" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="112" ht="390" customHeight="true">
+    <row r="112" ht="409" customHeight="true">
       <c r="A112" s="30" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="113" ht="390" customHeight="true">
+    <row r="113" ht="409" customHeight="true">
       <c r="A113" s="30" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="114" ht="390" customHeight="true">
+    <row r="114" ht="409" customHeight="true">
       <c r="A114" s="30" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="115" ht="390" customHeight="true">
+    <row r="115" ht="409" customHeight="true">
       <c r="A115" s="30" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="116" ht="390" customHeight="true">
+    <row r="116" ht="409" customHeight="true">
       <c r="A116" s="30" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="117" ht="390" customHeight="true">
+    <row r="117" ht="409" customHeight="true">
       <c r="A117" s="30" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="118" ht="390" customHeight="true">
+    <row r="118" ht="409" customHeight="true">
       <c r="A118" s="30" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="119" ht="390" customHeight="true">
+    <row r="119" ht="409" customHeight="true">
       <c r="A119" s="30" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="120" ht="390" customHeight="true">
+    <row r="120" ht="409" customHeight="true">
       <c r="A120" s="30" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="121" ht="390" customHeight="true">
+    <row r="121" ht="409" customHeight="true">
       <c r="A121" s="30" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="122" ht="390" customHeight="true">
+    <row r="122" ht="409" customHeight="true">
       <c r="A122" s="30" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="123" ht="390" customHeight="true">
+    <row r="123" ht="409" customHeight="true">
       <c r="A123" s="30" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="124" ht="390" customHeight="true">
+    <row r="124" ht="409" customHeight="true">
       <c r="A124" s="30" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="125" ht="390" customHeight="true">
+    <row r="125" ht="409" customHeight="true">
       <c r="A125" s="30" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="126" ht="390" customHeight="true">
+    <row r="126" ht="409" customHeight="true">
       <c r="A126" s="30" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="127" ht="390" customHeight="true">
+    <row r="127" ht="409" customHeight="true">
       <c r="A127" s="30" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="128" ht="390" customHeight="true">
+    <row r="128" ht="409" customHeight="true">
       <c r="A128" s="30" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="129" ht="390" customHeight="true">
+    <row r="129" ht="409" customHeight="true">
       <c r="A129" s="30" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="130" ht="390" customHeight="true">
+    <row r="130" ht="409" customHeight="true">
       <c r="A130" s="30" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="131" ht="390" customHeight="true">
+    <row r="131" ht="409" customHeight="true">
       <c r="A131" s="30" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="132" ht="390" customHeight="true">
+    <row r="132" ht="409" customHeight="true">
       <c r="A132" s="30" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="133" ht="390" customHeight="true">
+    <row r="133" ht="409" customHeight="true">
       <c r="A133" s="30" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="134" ht="390" customHeight="true">
+    <row r="134" ht="409" customHeight="true">
       <c r="A134" s="30" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="135" ht="390" customHeight="true">
+    <row r="135" ht="409" customHeight="true">
       <c r="A135" s="30" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="136" ht="390" customHeight="true">
+    <row r="136" ht="409" customHeight="true">
       <c r="A136" s="30" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="137" ht="390" customHeight="true">
+    <row r="137" ht="409" customHeight="true">
       <c r="A137" s="30" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="138" ht="390" customHeight="true">
+    <row r="138" ht="409" customHeight="true">
       <c r="A138" s="30" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="139" ht="390" customHeight="true">
+    <row r="139" ht="409" customHeight="true">
       <c r="A139" s="30" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="140" ht="390" customHeight="true">
+    <row r="140" ht="409" customHeight="true">
       <c r="A140" s="30" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="141" ht="390" customHeight="true">
+    <row r="141" ht="409" customHeight="true">
       <c r="A141" s="30" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="142" ht="390" customHeight="true">
+    <row r="142" ht="409" customHeight="true">
       <c r="A142" s="30" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="143" ht="390" customHeight="true">
+    <row r="143" ht="409" customHeight="true">
       <c r="A143" s="30" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="144" ht="390" customHeight="true">
+    <row r="144" ht="409" customHeight="true">
       <c r="A144" s="30" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="145" ht="390" customHeight="true">
+    <row r="145" ht="409" customHeight="true">
       <c r="A145" s="30" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="146" ht="390" customHeight="true">
+    <row r="146" ht="409" customHeight="true">
       <c r="A146" s="30" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="147" ht="390" customHeight="true">
+    <row r="147" ht="409" customHeight="true">
       <c r="A147" s="30" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="148" ht="390" customHeight="true">
+    <row r="148" ht="409" customHeight="true">
       <c r="A148" s="30" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="149" ht="390" customHeight="true">
+    <row r="149" ht="409" customHeight="true">
       <c r="A149" s="30" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="150" ht="390" customHeight="true">
+    <row r="150" ht="409" customHeight="true">
       <c r="A150" s="30" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="151" ht="390" customHeight="true">
+    <row r="151" ht="409" customHeight="true">
       <c r="A151" s="30" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="152" ht="390" customHeight="true">
+    <row r="152" ht="409" customHeight="true">
       <c r="A152" s="30" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="153" ht="390" customHeight="true">
+    <row r="153" ht="409" customHeight="true">
       <c r="A153" s="30" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="154" ht="390" customHeight="true">
+    <row r="154" ht="409" customHeight="true">
       <c r="A154" s="30" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="155" ht="390" customHeight="true">
+    <row r="155" ht="409" customHeight="true">
       <c r="A155" s="30" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="156" ht="390" customHeight="true">
+    <row r="156" ht="409" customHeight="true">
       <c r="A156" s="30" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="157" ht="390" customHeight="true">
+    <row r="157" ht="409" customHeight="true">
       <c r="A157" s="30" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="158" ht="390" customHeight="true">
+    <row r="158" ht="409" customHeight="true">
       <c r="A158" s="30" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="159" ht="390" customHeight="true">
+    <row r="159" ht="409" customHeight="true">
       <c r="A159" s="30" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="160" ht="390" customHeight="true">
+    <row r="160" ht="409" customHeight="true">
       <c r="A160" s="30" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="161" ht="390" customHeight="true">
+    <row r="161" ht="409" customHeight="true">
       <c r="A161" s="30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="162" ht="390" customHeight="true">
+    <row r="162" ht="409" customHeight="true">
       <c r="A162" s="30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="163" ht="390" customHeight="true">
+    <row r="163" ht="409" customHeight="true">
       <c r="A163" s="30" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="164" ht="390" customHeight="true">
+    <row r="164" ht="409" customHeight="true">
       <c r="A164" s="30" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="165" ht="390" customHeight="true">
+    <row r="165" ht="409" customHeight="true">
       <c r="A165" s="30" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="166" ht="390" customHeight="true">
+    <row r="166" ht="409" customHeight="true">
       <c r="A166" s="30" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="167" ht="390" customHeight="true">
+    <row r="167" ht="409" customHeight="true">
       <c r="A167" s="30" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="168" ht="390" customHeight="true">
+    <row r="168" ht="409" customHeight="true">
       <c r="A168" s="30" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="169" ht="390" customHeight="true">
+    <row r="169" ht="409" customHeight="true">
       <c r="A169" s="30" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="170" ht="390" customHeight="true">
+    <row r="170" ht="409" customHeight="true">
       <c r="A170" s="30" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="171" ht="390" customHeight="true">
+    <row r="171" ht="409" customHeight="true">
       <c r="A171" s="30" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="172" ht="390" customHeight="true">
+    <row r="172" ht="409" customHeight="true">
       <c r="A172" s="30" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="173" ht="390" customHeight="true">
+    <row r="173" ht="409" customHeight="true">
       <c r="A173" s="30" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="174" ht="390" customHeight="true">
+    <row r="174" ht="409" customHeight="true">
       <c r="A174" s="30" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="175" ht="390" customHeight="true">
+    <row r="175" ht="409" customHeight="true">
       <c r="A175" s="30" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="176" ht="390" customHeight="true">
+    <row r="176" ht="409" customHeight="true">
       <c r="A176" s="30" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="177" ht="390" customHeight="true">
+    <row r="177" ht="409" customHeight="true">
       <c r="A177" s="30" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="178" ht="390" customHeight="true">
+    <row r="178" ht="409" customHeight="true">
       <c r="A178" s="30" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="179" ht="390" customHeight="true">
+    <row r="179" ht="409" customHeight="true">
       <c r="A179" s="30" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="180" ht="390" customHeight="true">
+    <row r="180" ht="409" customHeight="true">
       <c r="A180" s="30" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="181" ht="390" customHeight="true">
+    <row r="181" ht="409" customHeight="true">
       <c r="A181" s="30" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="182" ht="390" customHeight="true">
+    <row r="182" ht="409" customHeight="true">
       <c r="A182" s="30" t="s">
         <v>343</v>
       </c>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -1367,7 +1367,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4727,7 +4727,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -23,6 +23,10 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$71</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$269</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$K$43</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$K$42</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Tree 3'!$A$1:$K$43</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Tree 4'!$A$1:$K$37</definedName>
     <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$47</definedName>
     <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$44</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$279</definedName>
@@ -3178,12 +3182,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3200,11 +3209,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -3556,20 +3560,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3586,11 +3595,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -3923,10 +3927,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -14772,12 +14776,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14794,11 +14803,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -15150,20 +15154,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15180,11 +15189,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -15540,9 +15544,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -1565,7 +1565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -3224,6 +3224,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$51</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
@@ -14818,6 +14820,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -3227,7 +3227,7 @@
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="7">
@@ -3248,7 +3248,7 @@
         <f>'data'!$A$55</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3271,7 +3271,7 @@
         <f>"2. " &amp; data!$B$54</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3288,7 +3288,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3310,7 +3310,7 @@
         <f>"1. " &amp; data!$B$56</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3335,7 +3335,7 @@
         <f>"3. " &amp; data!$B$58</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3355,7 +3355,7 @@
         <f>'data'!$A$61</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3374,7 +3374,7 @@
         <f>"2. " &amp; data!$B$60</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3391,7 +3391,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G152)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3413,7 +3413,7 @@
         <f>"1. " &amp; data!$B$62</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G168)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3438,7 +3438,7 @@
         <f>"3. " &amp; data!$B$64</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G186)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3458,7 +3458,7 @@
         <f>'data'!$A$67</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G202)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3477,7 +3477,7 @@
         <f>"2. " &amp; data!$B$66</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G220)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3498,7 +3498,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G236)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3518,7 +3518,7 @@
         <f>"1. " &amp; data!$B$68</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G254)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3608,7 +3608,7 @@
         <f>"1. " &amp; data!$B$74</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G267)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
       </c>
     </row>
     <row r="6">
@@ -3625,7 +3625,7 @@
         <f>"3. " &amp; data!$B$76</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -3643,7 +3643,7 @@
         <f>'data'!$A$79</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O168)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3666,7 +3666,7 @@
         <f>"2. " &amp; data!$B$78</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G152)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3683,7 +3683,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O185)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3705,7 +3705,7 @@
         <f>"1. " &amp; data!$B$80</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G169)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3730,7 +3730,7 @@
         <f>"3. " &amp; data!$B$82</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3750,7 +3750,7 @@
         <f>'data'!$A$85</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G186)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3769,7 +3769,7 @@
         <f>"2. " &amp; data!$B$84</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3786,7 +3786,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O152)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G203)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3808,7 +3808,7 @@
         <f>"1. " &amp; data!$B$86</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O168)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3833,7 +3833,7 @@
         <f>"3. " &amp; data!$B$88</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O186)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G220)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3853,7 +3853,7 @@
         <f>'data'!$A$91</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3872,7 +3872,7 @@
         <f>"2. " &amp; data!$B$90</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G237)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3893,7 +3893,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G254)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3913,7 +3913,7 @@
         <f>"1. " &amp; data!$B$92</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G268)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -12169,7 +12169,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -12177,10 +12177,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -12188,7 +12188,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="6">
@@ -12253,7 +12253,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -12261,10 +12261,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -12272,7 +12272,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
       </c>
     </row>
     <row r="14">
@@ -12337,7 +12337,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -12345,10 +12345,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -12356,7 +12356,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
       </c>
     </row>
     <row r="22">
@@ -12421,7 +12421,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -12429,10 +12429,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G152)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -12440,7 +12440,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
       </c>
     </row>
     <row r="30">
@@ -12505,7 +12505,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G169)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -12513,10 +12513,10 @@
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G185)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G186)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
@@ -12524,7 +12524,7 @@
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G168)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
       </c>
     </row>
     <row r="38">
@@ -12589,7 +12589,7 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G203)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -12597,10 +12597,10 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G219)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
       </c>
       <c r="I44" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G220)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
@@ -12608,7 +12608,7 @@
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
       <c r="O44" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G202)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
       </c>
     </row>
     <row r="46">
@@ -12673,7 +12673,7 @@
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G237)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -12681,10 +12681,10 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G253)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
       </c>
       <c r="I52" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G254)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
       </c>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
@@ -12692,7 +12692,7 @@
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G236)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
       </c>
     </row>
     <row r="54">
@@ -12757,7 +12757,7 @@
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G268)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -12765,10 +12765,10 @@
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
       <c r="G60" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
       </c>
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
@@ -12776,7 +12776,7 @@
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
       <c r="O60" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G267)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
       </c>
     </row>
     <row r="62">
@@ -12841,7 +12841,7 @@
     </row>
     <row r="68">
       <c r="A68" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O152)</f>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -12849,10 +12849,10 @@
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="G68" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G168)</f>
       </c>
       <c r="I68" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G152)</f>
       </c>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
@@ -12860,7 +12860,7 @@
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
       <c r="O68" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O168)</f>
       </c>
     </row>
     <row r="70">
@@ -12925,7 +12925,7 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O169)</f>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -12933,10 +12933,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G185)</f>
       </c>
       <c r="I76" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G169)</f>
       </c>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
@@ -12944,7 +12944,7 @@
       <c r="M76" s="18"/>
       <c r="N76" s="18"/>
       <c r="O76" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O185)</f>
       </c>
     </row>
     <row r="78">
@@ -13009,7 +13009,7 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O186)</f>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -13017,10 +13017,10 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G202)</f>
       </c>
       <c r="I84" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G186)</f>
       </c>
       <c r="J84" s="18"/>
       <c r="K84" s="18"/>
@@ -13028,7 +13028,7 @@
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
       </c>
     </row>
     <row r="86">
@@ -13093,7 +13093,7 @@
     </row>
     <row r="92">
       <c r="A92" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -13101,10 +13101,10 @@
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
       <c r="G92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G219)</f>
       </c>
       <c r="I92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O152)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G203)</f>
       </c>
       <c r="J92" s="18"/>
       <c r="K92" s="18"/>
@@ -13112,7 +13112,7 @@
       <c r="M92" s="18"/>
       <c r="N92" s="18"/>
       <c r="O92" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
       </c>
     </row>
     <row r="94">
@@ -13177,7 +13177,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O169)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -13185,10 +13185,10 @@
       <c r="E100" s="18"/>
       <c r="F100" s="18"/>
       <c r="G100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O185)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G236)</f>
       </c>
       <c r="I100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O186)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G220)</f>
       </c>
       <c r="J100" s="18"/>
       <c r="K100" s="18"/>
@@ -13196,7 +13196,7 @@
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O168)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
       </c>
     </row>
     <row r="102">
@@ -13261,7 +13261,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13269,10 +13269,10 @@
       <c r="E108" s="18"/>
       <c r="F108" s="18"/>
       <c r="G108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G253)</f>
       </c>
       <c r="I108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G237)</f>
       </c>
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
@@ -13280,7 +13280,7 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
       </c>
     </row>
     <row r="110">
@@ -13345,7 +13345,7 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -13353,10 +13353,10 @@
       <c r="E116" s="18"/>
       <c r="F116" s="18"/>
       <c r="G116" s="14" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G267)</f>
       </c>
       <c r="I116" s="14" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G268)</f>
       </c>
       <c r="J116" s="18"/>
       <c r="K116" s="18"/>
@@ -13364,7 +13364,7 @@
       <c r="M116" s="18"/>
       <c r="N116" s="18"/>
       <c r="O116" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G254)</f>
       </c>
     </row>
     <row r="118">
@@ -13448,7 +13448,7 @@
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
       <c r="O129" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="131">
@@ -14844,7 +14844,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -14867,7 +14867,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -14884,7 +14884,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -14906,7 +14906,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -14931,7 +14931,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -14951,7 +14951,7 @@
         <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -14970,7 +14970,7 @@
         <f>"2. " &amp; data!$B$13</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -14987,7 +14987,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15009,7 +15009,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G185)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -15034,7 +15034,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G169)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15054,7 +15054,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G219)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -15073,7 +15073,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G203)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15094,7 +15094,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G253)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -15114,7 +15114,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G237)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -15204,7 +15204,7 @@
         <f>"1. " &amp; data!$B$27</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
       </c>
     </row>
     <row r="6">
@@ -15221,7 +15221,7 @@
         <f>"3. " &amp; data!$B$29</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G268)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -15239,7 +15239,7 @@
         <f>'data'!$A$32</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G168)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -15262,7 +15262,7 @@
         <f>"2. " &amp; data!$B$31</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O152)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -15279,7 +15279,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G185)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -15301,7 +15301,7 @@
         <f>"1. " &amp; data!$B$33</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O169)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -15326,7 +15326,7 @@
         <f>"3. " &amp; data!$B$35</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G202)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -15346,7 +15346,7 @@
         <f>'data'!$A$38</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O186)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -15365,7 +15365,7 @@
         <f>"2. " &amp; data!$B$37</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G219)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -15382,7 +15382,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15404,7 +15404,7 @@
         <f>"1. " &amp; data!$B$39</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O185)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G236)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -15429,7 +15429,7 @@
         <f>"3. " &amp; data!$B$41</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O169)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15449,7 +15449,7 @@
         <f>'data'!$A$44</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G253)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -15468,7 +15468,7 @@
         <f>"2. " &amp; data!$B$43</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15489,7 +15489,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G267)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -15509,7 +15509,7 @@
         <f>"1. " &amp; data!$B$45</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -3219,21 +3219,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$50</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$51</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$52</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -3260,7 +3267,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3271,7 +3278,7 @@
         <f>"2. " &amp; data!$B$54</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3300,7 +3307,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3310,7 +3317,7 @@
         <f>"1. " &amp; data!$B$56</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3344,7 +3351,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3355,7 +3362,7 @@
         <f>'data'!$A$61</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3384,14 +3391,14 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="20"/>
     </row>
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3426,7 +3433,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3438,7 +3445,7 @@
         <f>"3. " &amp; data!$B$64</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3468,7 +3475,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3477,7 +3484,7 @@
         <f>"2. " &amp; data!$B$66</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3508,7 +3515,7 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -3518,7 +3525,7 @@
         <f>"1. " &amp; data!$B$68</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3607,28 +3614,21 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$74</f>
       </c>
-      <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$75</f>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="21">
-        <v>23</v>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23" t="str">
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$76</f>
       </c>
-      <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -12177,7 +12177,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
       <c r="I4" s="14" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
@@ -12188,7 +12188,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="6">
@@ -12261,7 +12261,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="I12" s="14" t="str">
         <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
@@ -12272,7 +12272,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="14">
@@ -12345,7 +12345,7 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I20" s="14" t="str">
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
@@ -12356,7 +12356,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O49)</f>
       </c>
     </row>
     <row r="22">
@@ -12429,7 +12429,7 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I28" s="14" t="str">
         <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
@@ -12440,7 +12440,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O66)</f>
       </c>
     </row>
     <row r="30">
@@ -12513,7 +12513,7 @@
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G83)</f>
       </c>
       <c r="I36" s="14" t="str">
         <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G84)</f>
@@ -12524,7 +12524,7 @@
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O83)</f>
       </c>
     </row>
     <row r="38">
@@ -12597,7 +12597,7 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G100)</f>
       </c>
       <c r="I44" s="14" t="str">
         <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G101)</f>
@@ -12608,7 +12608,7 @@
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
       <c r="O44" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O100)</f>
       </c>
     </row>
     <row r="46">
@@ -12681,7 +12681,7 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G117)</f>
       </c>
       <c r="I52" s="14" t="str">
         <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G118)</f>
@@ -12692,7 +12692,7 @@
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O117)</f>
       </c>
     </row>
     <row r="54">
@@ -12765,7 +12765,7 @@
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
       <c r="G60" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G134)</f>
       </c>
       <c r="I60" s="14" t="str">
         <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G135)</f>
@@ -12776,7 +12776,7 @@
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
       <c r="O60" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O134)</f>
       </c>
     </row>
     <row r="62">
@@ -13429,7 +13429,7 @@
     </row>
     <row r="129">
       <c r="A129" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G6)</f>
+        <f>CONCATENATE("M 2 ",G14)</f>
       </c>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -13437,10 +13437,10 @@
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
       <c r="G129" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
+        <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I129" s="14" t="str">
-        <f>CONCATENATE("M 16 ",O6)</f>
+        <f>CONCATENATE("M 17 ",O14)</f>
       </c>
       <c r="J129" s="18"/>
       <c r="K129" s="18"/>
@@ -13448,7 +13448,7 @@
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
       <c r="O129" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("M 16 ",O6)</f>
       </c>
     </row>
     <row r="131">
@@ -13513,7 +13513,7 @@
     </row>
     <row r="137">
       <c r="A137" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G22)</f>
+        <f>CONCATENATE("M 4 ",G30)</f>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -13521,10 +13521,10 @@
       <c r="E137" s="18"/>
       <c r="F137" s="18"/>
       <c r="G137" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G14)</f>
+        <f>CONCATENATE("M 3 ",G22)</f>
       </c>
       <c r="I137" s="14" t="str">
-        <f>CONCATENATE("M 18 ",O22)</f>
+        <f>CONCATENATE("M 19 ",O30)</f>
       </c>
       <c r="J137" s="18"/>
       <c r="K137" s="18"/>
@@ -13532,7 +13532,7 @@
       <c r="M137" s="18"/>
       <c r="N137" s="18"/>
       <c r="O137" s="14" t="str">
-        <f>CONCATENATE("M 17 ",O14)</f>
+        <f>CONCATENATE("M 18 ",O22)</f>
       </c>
     </row>
     <row r="139">
@@ -13597,7 +13597,7 @@
     </row>
     <row r="145">
       <c r="A145" s="14" t="str">
-        <f>CONCATENATE("M 5 ",G38)</f>
+        <f>CONCATENATE("M 6 ",G46)</f>
       </c>
       <c r="B145" s="18"/>
       <c r="C145" s="18"/>
@@ -13605,10 +13605,10 @@
       <c r="E145" s="18"/>
       <c r="F145" s="18"/>
       <c r="G145" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G30)</f>
+        <f>CONCATENATE("M 5 ",G38)</f>
       </c>
       <c r="I145" s="14" t="str">
-        <f>CONCATENATE("M 20 ",O38)</f>
+        <f>CONCATENATE("M 21 ",O46)</f>
       </c>
       <c r="J145" s="18"/>
       <c r="K145" s="18"/>
@@ -13616,7 +13616,7 @@
       <c r="M145" s="18"/>
       <c r="N145" s="18"/>
       <c r="O145" s="14" t="str">
-        <f>CONCATENATE("M 19 ",O30)</f>
+        <f>CONCATENATE("M 20 ",O38)</f>
       </c>
     </row>
     <row r="147">
@@ -13681,7 +13681,7 @@
     </row>
     <row r="153">
       <c r="A153" s="14" t="str">
-        <f>CONCATENATE("M 7 ",G54)</f>
+        <f>CONCATENATE("M 8 ",G62)</f>
       </c>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -13689,10 +13689,10 @@
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
       <c r="G153" s="14" t="str">
-        <f>CONCATENATE("M 6 ",G46)</f>
+        <f>CONCATENATE("M 7 ",G54)</f>
       </c>
       <c r="I153" s="14" t="str">
-        <f>CONCATENATE("M 22 ",O54)</f>
+        <f>CONCATENATE("M 23 ",O62)</f>
       </c>
       <c r="J153" s="18"/>
       <c r="K153" s="18"/>
@@ -13700,7 +13700,7 @@
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
       <c r="O153" s="14" t="str">
-        <f>CONCATENATE("M 21 ",O46)</f>
+        <f>CONCATENATE("M 22 ",O54)</f>
       </c>
     </row>
     <row r="155">
@@ -13773,7 +13773,7 @@
       <c r="E161" s="18"/>
       <c r="F161" s="18"/>
       <c r="G161" s="14" t="str">
-        <f>CONCATENATE("M 8 ",G62)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
       </c>
       <c r="I161" s="14" t="str">
         <f>CONCATENATE("M 24 ",O70)</f>
@@ -13784,7 +13784,7 @@
       <c r="M161" s="18"/>
       <c r="N161" s="18"/>
       <c r="O161" s="14" t="str">
-        <f>CONCATENATE("M 23 ",O62)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O151)</f>
       </c>
     </row>
     <row r="163">
@@ -14815,21 +14815,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -14856,7 +14863,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -14867,7 +14874,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -14896,7 +14903,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -14906,7 +14913,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -14940,7 +14947,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -14951,7 +14958,7 @@
         <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -14980,14 +14987,14 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="20"/>
     </row>
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O67)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15022,7 +15029,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -15034,7 +15041,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O84)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15064,7 +15071,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -15073,7 +15080,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O101)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15104,7 +15111,7 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -15114,7 +15121,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O118)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -15203,28 +15210,21 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$27</f>
       </c>
-      <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$28</f>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="21">
-        <v>8</v>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23" t="str">
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G151)</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$29</f>
       </c>
-      <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O135)</f>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -89,187 +89,616 @@
     <t>Pool A</t>
   </si>
   <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>Elijah Taylor</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>TAYLOR</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>Team Alpha</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>THOMPSON</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Kaden Martin</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>Sylvia Plath</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>PLATH</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
     <t>Kevin Clark</t>
   </si>
   <si>
-    <t>Team Alpha</t>
-  </si>
-  <si>
     <t>CLARK</t>
   </si>
   <si>
+    <t>Pool I</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Pool J</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Pool K</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool L</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool M</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool N</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool O</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>Cersei Lannister</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool P</t>
+  </si>
+  <si>
     <t>Owen Rodriguez</t>
   </si>
   <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
+  </si>
+  <si>
+    <t>Pool Q</t>
+  </si>
+  <si>
+    <t>Luke Rodriguez</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
   </si>
   <si>
     <t>Voldemort</t>
   </si>
   <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
     <t>VOLDEMORT</t>
   </si>
   <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>THOMPSON</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
+    <t>Pool R</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>Pool S</t>
+  </si>
+  <si>
+    <t>Liam Thompson</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>Pool T</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>Pool U</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>Pool V</t>
+  </si>
+  <si>
+    <t>Xavier Scott</t>
+  </si>
+  <si>
+    <t>SCOTT</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>Pool W</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>Thomas Hardy</t>
+  </si>
+  <si>
+    <t>HARDY</t>
+  </si>
+  <si>
+    <t>Pool X</t>
+  </si>
+  <si>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Pool Y</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
   </si>
   <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
     <t>EVERDEEN</t>
   </si>
   <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>Pool Z</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
   </si>
   <si>
     <t>Moby Dick</t>
   </si>
   <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
+    <t>Pool AA</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
   </si>
   <si>
     <t>Othello</t>
   </si>
   <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
     <t>OTHELLO</t>
   </si>
   <si>
-    <t>Pool H</t>
+    <t>Pool BB</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Pool CC</t>
   </si>
   <si>
     <t>Benjamin Evans</t>
@@ -278,472 +707,43 @@
     <t>EVANS</t>
   </si>
   <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Pool I</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool J</t>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>Pool DD</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool EE</t>
   </si>
   <si>
     <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool K</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Pool L</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool M</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool N</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>Pool O</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Pool P</t>
-  </si>
-  <si>
-    <t>Elijah Taylor</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>Pool Q</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>Pool R</t>
-  </si>
-  <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>Pool S</t>
-  </si>
-  <si>
-    <t>Kaden Martin</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>Pool T</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>Pool U</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>Pool V</t>
-  </si>
-  <si>
-    <t>Luke Rodriguez</t>
-  </si>
-  <si>
-    <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>Pool W</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>Pool X</t>
-  </si>
-  <si>
-    <t>Liam Thompson</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Pool Y</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>Pool Z</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>Pool AA</t>
-  </si>
-  <si>
-    <t>Xavier Scott</t>
-  </si>
-  <si>
-    <t>SCOTT</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>Pool BB</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Sylvia Plath</t>
-  </si>
-  <si>
-    <t>PLATH</t>
-  </si>
-  <si>
-    <t>Pool CC</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>Thomas Hardy</t>
-  </si>
-  <si>
-    <t>HARDY</t>
-  </si>
-  <si>
-    <t>Pool DD</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
-  </si>
-  <si>
-    <t>Pool EE</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
   </si>
   <si>
     <t>Parker Lewis</t>
@@ -1951,10 +1951,10 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -1962,13 +1962,13 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1976,214 +1976,214 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
         <v>74</v>
@@ -2203,10 +2203,10 @@
         <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -2214,13 +2214,13 @@
         <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
@@ -2228,38 +2228,38 @@
         <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
         <v>90</v>
@@ -2267,41 +2267,41 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
         <v>91</v>
       </c>
       <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
         <v>92</v>
-      </c>
-      <c r="D29" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
         <v>94</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
         <v>95</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
         <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
         <v>97</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -2329,10 +2329,10 @@
         <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
@@ -2340,13 +2340,13 @@
         <v>101</v>
       </c>
       <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
         <v>104</v>
-      </c>
-      <c r="C34" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="35">
@@ -2354,584 +2354,584 @@
         <v>101</v>
       </c>
       <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" t="s">
         <v>107</v>
-      </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" t="s">
         <v>110</v>
-      </c>
-      <c r="B36" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
         <v>118</v>
       </c>
-      <c r="B40" t="s">
-        <v>121</v>
-      </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" t="s">
         <v>127</v>
       </c>
-      <c r="B43" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" t="s">
-        <v>122</v>
-      </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" t="s">
         <v>135</v>
       </c>
-      <c r="B46" t="s">
-        <v>137</v>
-      </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
         <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" t="s">
         <v>142</v>
       </c>
-      <c r="B49" t="s">
-        <v>145</v>
-      </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" t="s">
         <v>147</v>
       </c>
-      <c r="B50" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" t="s">
-        <v>18</v>
-      </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B52" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" t="s">
         <v>151</v>
-      </c>
-      <c r="C52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" t="s">
         <v>153</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" t="s">
         <v>154</v>
-      </c>
-      <c r="C53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B54" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54" t="s">
         <v>156</v>
-      </c>
-      <c r="C54" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B55" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" t="s">
         <v>158</v>
-      </c>
-      <c r="C55" t="s">
-        <v>41</v>
-      </c>
-      <c r="D55" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" t="s">
         <v>160</v>
       </c>
-      <c r="B56" t="s">
-        <v>161</v>
-      </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>162</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B58" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D58" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D59" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" t="s">
         <v>167</v>
       </c>
-      <c r="B60" t="s">
-        <v>170</v>
-      </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="D60" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C61" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="D61" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="D62" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B63" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" t="s">
         <v>174</v>
       </c>
-      <c r="B64" t="s">
-        <v>178</v>
-      </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" t="s">
+        <v>127</v>
+      </c>
+      <c r="D66" t="s">
         <v>180</v>
-      </c>
-      <c r="B66" t="s">
-        <v>182</v>
-      </c>
-      <c r="C66" t="s">
-        <v>38</v>
-      </c>
-      <c r="D66" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B67" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D67" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>183</v>
+      </c>
+      <c r="B69" t="s">
         <v>185</v>
       </c>
-      <c r="B69" t="s">
-        <v>187</v>
-      </c>
       <c r="C69" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D69" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B70" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="D70" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C71" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" t="s">
         <v>191</v>
       </c>
-      <c r="B72" t="s">
-        <v>193</v>
-      </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="D73" t="s">
-        <v>58</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>195</v>
+      </c>
+      <c r="B74" t="s">
         <v>196</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>147</v>
+      </c>
+      <c r="D74" t="s">
         <v>197</v>
-      </c>
-      <c r="C74" t="s">
-        <v>69</v>
-      </c>
-      <c r="D74" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B75" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" t="s">
         <v>199</v>
-      </c>
-      <c r="C75" t="s">
-        <v>89</v>
-      </c>
-      <c r="D75" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B76" t="s">
         <v>200</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
         <v>201</v>
@@ -2945,7 +2945,7 @@
         <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D77" t="s">
         <v>204</v>
@@ -2959,10 +2959,10 @@
         <v>205</v>
       </c>
       <c r="C78" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79">
@@ -2970,136 +2970,136 @@
         <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C79" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="D79" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>207</v>
+      </c>
+      <c r="B80" t="s">
+        <v>208</v>
+      </c>
+      <c r="C80" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" t="s">
         <v>209</v>
-      </c>
-      <c r="B80" t="s">
-        <v>210</v>
-      </c>
-      <c r="C80" t="s">
-        <v>103</v>
-      </c>
-      <c r="D80" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B81" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="D81" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C82" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="D82" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>213</v>
+      </c>
+      <c r="B83" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" t="s">
         <v>215</v>
-      </c>
-      <c r="B83" t="s">
-        <v>216</v>
-      </c>
-      <c r="C83" t="s">
-        <v>103</v>
-      </c>
-      <c r="D83" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B84" t="s">
+        <v>216</v>
+      </c>
+      <c r="C84" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" t="s">
         <v>217</v>
-      </c>
-      <c r="C84" t="s">
-        <v>105</v>
-      </c>
-      <c r="D84" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" t="s">
         <v>219</v>
-      </c>
-      <c r="C85" t="s">
-        <v>125</v>
-      </c>
-      <c r="D85" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>220</v>
+      </c>
+      <c r="B86" t="s">
         <v>221</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>147</v>
+      </c>
+      <c r="D86" t="s">
         <v>222</v>
-      </c>
-      <c r="C86" t="s">
-        <v>103</v>
-      </c>
-      <c r="D86" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B87" t="s">
+        <v>223</v>
+      </c>
+      <c r="C87" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" t="s">
         <v>224</v>
-      </c>
-      <c r="C87" t="s">
-        <v>122</v>
-      </c>
-      <c r="D87" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B88" t="s">
         <v>225</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="D88" t="s">
         <v>226</v>
@@ -3113,10 +3113,10 @@
         <v>228</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D89" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
     </row>
     <row r="90">
@@ -3124,13 +3124,13 @@
         <v>227</v>
       </c>
       <c r="B90" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="D90" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91">
@@ -3138,32 +3138,32 @@
         <v>227</v>
       </c>
       <c r="B91" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C91" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D91" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B92" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="D92" t="s">
-        <v>235</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B93" t="s">
         <v>236</v>
@@ -3172,7 +3172,7 @@
         <v>24</v>
       </c>
       <c r="D93" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -89,664 +89,664 @@
     <t>Pool A</t>
   </si>
   <si>
+    <t>Kaden Martin</t>
+  </si>
+  <si>
+    <t>Team Alpha</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>CLARK</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Kevin Clark</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Xavier Scott</t>
+  </si>
+  <si>
+    <t>SCOTT</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>Pool I</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
+  </si>
+  <si>
+    <t>Pool J</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>Pool K</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Pool L</t>
+  </si>
+  <si>
+    <t>Owen Rodriguez</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool M</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>Pool N</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>Pool O</t>
+  </si>
+  <si>
+    <t>Liam Thompson</t>
+  </si>
+  <si>
+    <t>THOMPSON</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool P</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>Pool Q</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>Pool R</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>Pool S</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>Luke Rodriguez</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>Pool T</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool U</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool V</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Pool W</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>Pool X</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
     <t>Nathaniel Hawthorne</t>
   </si>
   <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
     <t>HAWTHORNE</t>
   </si>
   <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Pool Y</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Pool Z</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Pool AA</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Pool BB</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Pool CC</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>Bilbo Baggins</t>
+  </si>
+  <si>
+    <t>Pool DD</t>
+  </si>
+  <si>
     <t>Elijah Taylor</t>
   </si>
   <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
     <t>TAYLOR</t>
   </si>
   <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>Team Alpha</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>THOMPSON</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Kaden Martin</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
     <t>Sylvia Plath</t>
   </si>
   <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
     <t>PLATH</t>
   </si>
   <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>Kevin Clark</t>
-  </si>
-  <si>
-    <t>CLARK</t>
-  </si>
-  <si>
-    <t>Pool I</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Pool J</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Pool K</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Pool L</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Pool M</t>
-  </si>
-  <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool N</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool O</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
     <t>Cersei Lannister</t>
   </si>
   <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool P</t>
-  </si>
-  <si>
-    <t>Owen Rodriguez</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>Pool Q</t>
-  </si>
-  <si>
-    <t>Luke Rodriguez</t>
-  </si>
-  <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool R</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>Pool S</t>
-  </si>
-  <si>
-    <t>Liam Thompson</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>Pool T</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>Pool U</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>Pool V</t>
-  </si>
-  <si>
-    <t>Xavier Scott</t>
-  </si>
-  <si>
-    <t>SCOTT</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>Pool W</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
+    <t>Pool EE</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
   </si>
   <si>
     <t>Thomas Hardy</t>
   </si>
   <si>
     <t>HARDY</t>
-  </si>
-  <si>
-    <t>Pool X</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Pool Y</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Pool Z</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Pool AA</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Pool BB</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool CC</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Pool DD</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool EE</t>
-  </si>
-  <si>
-    <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>Parker Lewis</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1993,10 +1993,10 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -2004,13 +2004,13 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -2018,629 +2018,629 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
@@ -2651,10 +2651,10 @@
         <v>160</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="D56" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57">
@@ -2662,13 +2662,13 @@
         <v>159</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58">
@@ -2679,7 +2679,7 @@
         <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
         <v>164</v>
@@ -2693,10 +2693,10 @@
         <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60">
@@ -2704,13 +2704,13 @@
         <v>165</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61">
@@ -2721,7 +2721,7 @@
         <v>169</v>
       </c>
       <c r="C61" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="D61" t="s">
         <v>170</v>
@@ -2735,10 +2735,10 @@
         <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63">
@@ -2749,10 +2749,10 @@
         <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
@@ -2763,7 +2763,7 @@
         <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
         <v>175</v>
@@ -2777,7 +2777,7 @@
         <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
         <v>178</v>
@@ -2791,10 +2791,10 @@
         <v>179</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67">
@@ -2802,181 +2802,181 @@
         <v>176</v>
       </c>
       <c r="B67" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" t="s">
         <v>181</v>
-      </c>
-      <c r="C67" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" t="s">
         <v>183</v>
       </c>
-      <c r="B68" t="s">
-        <v>184</v>
-      </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C69" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C71" t="s">
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" t="s">
+        <v>93</v>
+      </c>
+      <c r="D72" t="s">
         <v>191</v>
-      </c>
-      <c r="C72" t="s">
-        <v>24</v>
-      </c>
-      <c r="D72" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B73" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" t="s">
         <v>193</v>
-      </c>
-      <c r="C73" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" t="s">
         <v>195</v>
       </c>
-      <c r="B74" t="s">
-        <v>196</v>
-      </c>
       <c r="C74" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s">
-        <v>197</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D75" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B76" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D76" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" t="s">
+        <v>201</v>
+      </c>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" t="s">
         <v>202</v>
-      </c>
-      <c r="B77" t="s">
-        <v>203</v>
-      </c>
-      <c r="C77" t="s">
-        <v>79</v>
-      </c>
-      <c r="D77" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B78" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="D78" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
+        <v>205</v>
+      </c>
+      <c r="C79" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" t="s">
         <v>206</v>
-      </c>
-      <c r="C79" t="s">
-        <v>42</v>
-      </c>
-      <c r="D79" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -2987,7 +2987,7 @@
         <v>208</v>
       </c>
       <c r="C80" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s">
         <v>209</v>
@@ -3001,10 +3001,10 @@
         <v>210</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82">
@@ -3012,38 +3012,38 @@
         <v>207</v>
       </c>
       <c r="B82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C82" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B84" t="s">
         <v>216</v>
       </c>
       <c r="C84" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="D84" t="s">
         <v>217</v>
@@ -3051,13 +3051,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B85" t="s">
         <v>218</v>
       </c>
       <c r="C85" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D85" t="s">
         <v>219</v>
@@ -3071,7 +3071,7 @@
         <v>221</v>
       </c>
       <c r="C86" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="D86" t="s">
         <v>222</v>
@@ -3085,7 +3085,7 @@
         <v>223</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D87" t="s">
         <v>224</v>
@@ -3099,80 +3099,80 @@
         <v>225</v>
       </c>
       <c r="C88" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>226</v>
+      </c>
+      <c r="B89" t="s">
         <v>227</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" t="s">
         <v>228</v>
-      </c>
-      <c r="C89" t="s">
-        <v>79</v>
-      </c>
-      <c r="D89" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B90" t="s">
+        <v>229</v>
+      </c>
+      <c r="C90" t="s">
+        <v>64</v>
+      </c>
+      <c r="D90" t="s">
         <v>230</v>
-      </c>
-      <c r="C90" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B91" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="D91" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>232</v>
+      </c>
+      <c r="B92" t="s">
+        <v>233</v>
+      </c>
+      <c r="C92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" t="s">
         <v>234</v>
-      </c>
-      <c r="B92" t="s">
-        <v>235</v>
-      </c>
-      <c r="C92" t="s">
-        <v>147</v>
-      </c>
-      <c r="D92" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B93" t="s">
+        <v>235</v>
+      </c>
+      <c r="C93" t="s">
+        <v>52</v>
+      </c>
+      <c r="D93" t="s">
         <v>236</v>
-      </c>
-      <c r="C93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -29,6 +29,7 @@
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Tree 4'!$A$1:$K$37</definedName>
     <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$47</definedName>
     <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$44</definedName>
+    <definedName localSheetId="11" name="_xlnm.Print_Area">'Tags'!$A$1:$A$182</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$279</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -1584,13 +1585,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -5012,7 +5013,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -89,6 +89,54 @@
     <t>Pool A</t>
   </si>
   <si>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
     <t>Kaden Martin</t>
   </si>
   <si>
@@ -98,6 +146,69 @@
     <t>MARTIN</t>
   </si>
   <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>CLARK</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Kevin Clark</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>Jane Austen</t>
   </si>
   <si>
@@ -107,6 +218,15 @@
     <t>AUSTEN</t>
   </si>
   <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -116,103 +236,55 @@
     <t>QUIRRELL</t>
   </si>
   <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>CLARK</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
-  </si>
-  <si>
-    <t>Kevin Clark</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Xavier Scott</t>
+  </si>
+  <si>
+    <t>SCOTT</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>HALL</t>
   </si>
   <si>
     <t>Katniss Everdeen</t>
@@ -224,25 +296,46 @@
     <t>EVERDEEN</t>
   </si>
   <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>Pool I</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Pool J</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
   </si>
   <si>
     <t>Ron Weasley</t>
@@ -254,64 +347,64 @@
     <t>WEASLEY</t>
   </si>
   <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Xavier Scott</t>
-  </si>
-  <si>
-    <t>SCOTT</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Pool I</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
+    <t>Pool K</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Pool L</t>
+  </si>
+  <si>
+    <t>Owen Rodriguez</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool M</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
   </si>
   <si>
     <t>Neville Longbottom</t>
@@ -323,88 +416,13 @@
     <t>LONGBOTTOM</t>
   </si>
   <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>Pool J</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>Pool K</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Pool L</t>
-  </si>
-  <si>
-    <t>Owen Rodriguez</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool M</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
+    <t>Pool N</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>George Orwell</t>
@@ -413,24 +431,6 @@
     <t>ORWELL</t>
   </si>
   <si>
-    <t>Parker Lewis</t>
-  </si>
-  <si>
-    <t>Pool N</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>Uriel Wright</t>
   </si>
   <si>
@@ -446,303 +446,303 @@
     <t>THOMPSON</t>
   </si>
   <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool P</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>Pool Q</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>Pool R</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>Pool S</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>Luke Rodriguez</t>
+  </si>
+  <si>
+    <t>Elijah Taylor</t>
+  </si>
+  <si>
+    <t>TAYLOR</t>
+  </si>
+  <si>
+    <t>Pool T</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool U</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool V</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Pool W</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>Pool X</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Pool Y</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>Pool Z</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Pool AA</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Pool AB</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Pool AC</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>Bilbo Baggins</t>
+  </si>
+  <si>
+    <t>Pool AD</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>Sylvia Plath</t>
+  </si>
+  <si>
+    <t>PLATH</t>
+  </si>
+  <si>
+    <t>Cersei Lannister</t>
+  </si>
+  <si>
+    <t>Pool AE</t>
+  </si>
+  <si>
     <t>Zachary Adams</t>
   </si>
   <si>
     <t>ADAMS</t>
   </si>
   <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Pool P</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>Pool Q</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>Pool R</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>Pool S</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>Luke Rodriguez</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>Pool T</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Pool U</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool V</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool W</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>Pool X</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Pool Y</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Pool Z</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Pool AA</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Pool BB</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Pool CC</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>Pool DD</t>
-  </si>
-  <si>
-    <t>Elijah Taylor</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>Sylvia Plath</t>
-  </si>
-  <si>
-    <t>PLATH</t>
-  </si>
-  <si>
-    <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>Pool EE</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
     <t>Thomas Hardy</t>
   </si>
   <si>
@@ -1037,37 +1037,37 @@
     <t>AA3</t>
   </si>
   <si>
-    <t>BB1</t>
-  </si>
-  <si>
-    <t>BB2</t>
-  </si>
-  <si>
-    <t>BB3</t>
-  </si>
-  <si>
-    <t>CC1</t>
-  </si>
-  <si>
-    <t>CC2</t>
-  </si>
-  <si>
-    <t>CC3</t>
-  </si>
-  <si>
-    <t>DD1</t>
-  </si>
-  <si>
-    <t>DD2</t>
-  </si>
-  <si>
-    <t>DD3</t>
-  </si>
-  <si>
-    <t>EE1</t>
-  </si>
-  <si>
-    <t>EE2</t>
+    <t>AB1</t>
+  </si>
+  <si>
+    <t>AB2</t>
+  </si>
+  <si>
+    <t>AB3</t>
+  </si>
+  <si>
+    <t>AC1</t>
+  </si>
+  <si>
+    <t>AC2</t>
+  </si>
+  <si>
+    <t>AC3</t>
+  </si>
+  <si>
+    <t>AD1</t>
+  </si>
+  <si>
+    <t>AD2</t>
+  </si>
+  <si>
+    <t>AD3</t>
+  </si>
+  <si>
+    <t>AE1</t>
+  </si>
+  <si>
+    <t>AE2</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -2049,7 +2049,7 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
         <v>42</v>
@@ -2091,10 +2091,10 @@
         <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -2102,10 +2102,10 @@
         <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>61</v>
@@ -2147,304 +2147,304 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
         <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" t="s">
         <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
         <v>77</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
         <v>80</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>81</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>82</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
         <v>84</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
         <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
         <v>89</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
         <v>98</v>
       </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
-      </c>
       <c r="D31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" t="s">
         <v>105</v>
-      </c>
-      <c r="B33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
         <v>110</v>
-      </c>
-      <c r="C35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
         <v>113</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
         <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
         <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" t="s">
         <v>125</v>
-      </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="42">
@@ -2455,7 +2455,7 @@
         <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
         <v>128</v>
@@ -2469,7 +2469,7 @@
         <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
         <v>130</v>
@@ -2483,7 +2483,7 @@
         <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D44" t="s">
         <v>132</v>
@@ -2511,7 +2511,7 @@
         <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
         <v>137</v>
@@ -2539,7 +2539,7 @@
         <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
         <v>143</v>
@@ -2581,7 +2581,7 @@
         <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D51" t="s">
         <v>151</v>
@@ -2595,7 +2595,7 @@
         <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
         <v>153</v>
@@ -2623,10 +2623,10 @@
         <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55">
@@ -2634,10 +2634,10 @@
         <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s">
         <v>135</v>
@@ -2645,66 +2645,66 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
         <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="D59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
@@ -2715,80 +2715,80 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
         <v>145</v>
       </c>
       <c r="D61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B63" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
         <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
         <v>41</v>
@@ -2799,301 +2799,301 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s">
         <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="D71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B72" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="D72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C74" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B76" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C76" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C77" t="s">
         <v>28</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C79" t="s">
         <v>48</v>
       </c>
       <c r="D79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C80" t="s">
         <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C81" t="s">
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C83" t="s">
         <v>67</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D84" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B85" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C85" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C87" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>224</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B88" t="s">
         <v>225</v>
@@ -3102,7 +3102,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89">
@@ -3113,7 +3113,7 @@
         <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D89" t="s">
         <v>228</v>
@@ -3127,7 +3127,7 @@
         <v>229</v>
       </c>
       <c r="C90" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D90" t="s">
         <v>230</v>
@@ -3155,7 +3155,7 @@
         <v>233</v>
       </c>
       <c r="C92" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D92" t="s">
         <v>234</v>
@@ -3730,7 +3730,7 @@
         <f>"3. " &amp; data!$B$82</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
+        <f>CONCATENATE("Pool AB-1st ",'Pool Matches'!O202)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3769,7 +3769,7 @@
         <f>"2. " &amp; data!$B$84</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
+        <f>CONCATENATE("Pool AC-1st ",'Pool Matches'!O219)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3808,7 +3808,7 @@
         <f>"1. " &amp; data!$B$86</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O236)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3853,7 +3853,7 @@
         <f>'data'!$A$91</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
+        <f>CONCATENATE("Pool AE-1st ",'Pool Matches'!O252)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -13028,7 +13028,7 @@
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O202)</f>
+        <f>CONCATENATE("Pool AB-1st ",'Pool Matches'!O202)</f>
       </c>
     </row>
     <row r="86">
@@ -13093,7 +13093,7 @@
     </row>
     <row r="92">
       <c r="A92" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
+        <f>CONCATENATE("Pool AB-2nd ",'Pool Matches'!O203)</f>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -13112,7 +13112,7 @@
       <c r="M92" s="18"/>
       <c r="N92" s="18"/>
       <c r="O92" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O219)</f>
+        <f>CONCATENATE("Pool AC-1st ",'Pool Matches'!O219)</f>
       </c>
     </row>
     <row r="94">
@@ -13177,7 +13177,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
+        <f>CONCATENATE("Pool AC-2nd ",'Pool Matches'!O220)</f>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -13196,7 +13196,7 @@
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O236)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O236)</f>
       </c>
     </row>
     <row r="102">
@@ -13261,7 +13261,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O237)</f>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13280,7 +13280,7 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="14" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O252)</f>
+        <f>CONCATENATE("Pool AE-1st ",'Pool Matches'!O252)</f>
       </c>
     </row>
     <row r="110">
@@ -13345,7 +13345,7 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
+        <f>CONCATENATE("Pool AE-2nd ",'Pool Matches'!O253)</f>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -15382,7 +15382,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O203)</f>
+        <f>CONCATENATE("Pool AB-2nd ",'Pool Matches'!O203)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15429,7 +15429,7 @@
         <f>"3. " &amp; data!$B$41</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O220)</f>
+        <f>CONCATENATE("Pool AC-2nd ",'Pool Matches'!O220)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15468,7 +15468,7 @@
         <f>"2. " &amp; data!$B$43</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O237)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O237)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15509,7 +15509,7 @@
         <f>"1. " &amp; data!$B$45</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O253)</f>
+        <f>CONCATENATE("Pool AE-2nd ",'Pool Matches'!O253)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -1588,7 +1588,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -4220,8 +4220,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -4629,8 +4629,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-large-max-size.xlsx
+++ b/pools-example-large-max-size.xlsx
@@ -1591,7 +1591,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
